--- a/Areas_Paises.xlsx
+++ b/Areas_Paises.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uscp9a\Distribución OBS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{EA417238-0718-4DB6-9F47-3D23B1BA41A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7DEE916-8E88-4D4B-A028-75D1D1C8C8AF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E03CFD-D3C2-4BD9-85BF-A581898274A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{996CFF7E-4120-45EC-B5A3-4D8213062A4C}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Paises!$P$1:$V$225</definedName>
     <definedName name="PAISES">Paises!$A$1:$B$17</definedName>
     <definedName name="PILAR">Paises!$AF$1:$AG$18</definedName>
-    <definedName name="PROGRAMAS">Areas!$A$1:$G$46</definedName>
+    <definedName name="PROGRAMAS">Areas!$A$1:$G$45</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="555">
   <si>
     <t>PROGRAMA</t>
   </si>
@@ -316,18 +316,6 @@
   </si>
   <si>
     <t>VENTAS</t>
-  </si>
-  <si>
-    <t>Máster de Formación Permanente en Derecho Digital</t>
-  </si>
-  <si>
-    <t>Derecho Digital</t>
-  </si>
-  <si>
-    <t>Derecho Dig.</t>
-  </si>
-  <si>
-    <t>DERECHO DIG.</t>
   </si>
   <si>
     <t>Máster en Dirección de la Producción y Automatización Industrial</t>
@@ -2327,6 +2315,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2339,7 +2328,6 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Incorrecto" xfId="1" builtinId="27"/>
@@ -3687,8 +3675,8 @@
       <sheetName val="PROGRAMAS"/>
       <sheetName val="HISTORICO PROGRAMAS"/>
       <sheetName val="NORMALIZACION PROGRAMAS"/>
+      <sheetName val="RESUMEN PROG"/>
       <sheetName val="Hoja1"/>
-      <sheetName val="RESUMEN PROG"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -6366,9 +6354,129 @@
             <v>MKT EC</v>
           </cell>
         </row>
+        <row r="335">
+          <cell r="B335" t="str">
+            <v xml:space="preserve"> Máster en Dirección de la Producción y Automatización Industrial</v>
+          </cell>
+          <cell r="C335" t="str">
+            <v>PROD</v>
+          </cell>
+        </row>
+        <row r="336">
+          <cell r="B336" t="str">
+            <v xml:space="preserve">Lifelong Learning Master's Degree in Digital Marketing, E-Commerce and Artificial Intelligence </v>
+          </cell>
+          <cell r="C336" t="str">
+            <v>MKT EC ENG</v>
+          </cell>
+        </row>
+        <row r="337">
+          <cell r="B337" t="str">
+            <v xml:space="preserve">Máster de Formación Permanente en Dirección de Comunicación Corporativa </v>
+          </cell>
+          <cell r="C337" t="str">
+            <v>COMUNIC</v>
+          </cell>
+        </row>
+        <row r="338">
+          <cell r="B338" t="str">
+            <v>Máster de Formación Permanente en Dirección de Marketing y Gestión Comercial</v>
+          </cell>
+          <cell r="C338" t="str">
+            <v>MKT GC</v>
+          </cell>
+        </row>
+        <row r="339">
+          <cell r="B339" t="str">
+            <v xml:space="preserve">Máster de Formación Permanente en Executive MBA </v>
+          </cell>
+          <cell r="C339" t="str">
+            <v>EMBA ESP</v>
+          </cell>
+        </row>
+        <row r="340">
+          <cell r="B340" t="str">
+            <v>Máster de Formación Permanente en Responsabilidad Social Corporativa y Liderazgo Sostenible - Octubre 2025</v>
+          </cell>
+          <cell r="C340" t="str">
+            <v>RSC</v>
+          </cell>
+        </row>
+        <row r="341">
+          <cell r="B341" t="str">
+            <v>Máster de Formación Permanente en Transformación Digital -</v>
+          </cell>
+          <cell r="C341" t="str">
+            <v>TR DIGI</v>
+          </cell>
+        </row>
+        <row r="342">
+          <cell r="B342" t="str">
+            <v>Máster en formación permenante en responsabilidad social corporativa y liderazgo sostenible - abril 2025</v>
+          </cell>
+          <cell r="C342" t="str">
+            <v>RSC</v>
+          </cell>
+        </row>
+        <row r="343">
+          <cell r="B343" t="str">
+            <v>Responsabilidad Social Corporativa y Liderazgo Sostenible</v>
+          </cell>
+          <cell r="C343" t="str">
+            <v>RSC</v>
+          </cell>
+        </row>
+        <row r="344">
+          <cell r="B344" t="str">
+            <v xml:space="preserve">Máster en Dirección de la Producción y Automatización Industrial </v>
+          </cell>
+          <cell r="C344" t="str">
+            <v>PROD</v>
+          </cell>
+        </row>
+        <row r="345">
+          <cell r="B345" t="str">
+            <v xml:space="preserve">Máster de Formación Permanente en Dirección de Marketing y Gestión Comercial </v>
+          </cell>
+          <cell r="C345" t="str">
+            <v>MKT GC</v>
+          </cell>
+        </row>
+        <row r="346">
+          <cell r="B346" t="str">
+            <v>Máster en Dirección de la Producción y Automatización Industrial</v>
+          </cell>
+          <cell r="C346" t="str">
+            <v>PROD</v>
+          </cell>
+        </row>
+        <row r="347">
+          <cell r="B347" t="str">
+            <v>Máster de Formación Permanente en Responsabilidad Social Corporativa y Liderazgo Sostenible - Octubre 2025</v>
+          </cell>
+          <cell r="C347" t="str">
+            <v>RSC</v>
+          </cell>
+        </row>
+        <row r="348">
+          <cell r="B348" t="str">
+            <v xml:space="preserve">Máster de Formación Permanente en Machine Learning e Inteligencia Artificial </v>
+          </cell>
+          <cell r="C348" t="str">
+            <v>IA</v>
+          </cell>
+        </row>
+        <row r="349">
+          <cell r="B349" t="str">
+            <v xml:space="preserve">Máster en foormación Permanente en Business Intelligence y Analytics  </v>
+          </cell>
+          <cell r="C349" t="str">
+            <v>BI</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6762,17 +6870,17 @@
   <sheetData>
     <row r="1" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B1" s="27"/>
       <c r="D1" s="28" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="P1" s="29"/>
       <c r="Q1" s="29"/>
@@ -6797,8 +6905,8 @@
       <c r="AX1" s="35"/>
       <c r="AY1" s="35"/>
       <c r="BA1" s="35"/>
-      <c r="BC1" s="95"/>
-      <c r="BD1" s="95"/>
+      <c r="BC1" s="96"/>
+      <c r="BD1" s="96"/>
       <c r="BF1" s="28"/>
       <c r="BH1" s="28"/>
       <c r="BI1" s="28"/>
@@ -6818,19 +6926,19 @@
     </row>
     <row r="2" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A2" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F2" t="s">
         <v>176</v>
-      </c>
-      <c r="B2" s="40" t="s">
-        <v>177</v>
-      </c>
-      <c r="D2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E2" t="s">
-        <v>179</v>
-      </c>
-      <c r="F2" t="s">
-        <v>180</v>
       </c>
       <c r="P2" s="41"/>
       <c r="Q2" s="42"/>
@@ -6847,24 +6955,24 @@
       <c r="AP2" s="47"/>
       <c r="BC2" s="48"/>
       <c r="BF2" s="49"/>
-      <c r="BH2" s="93"/>
+      <c r="BH2" s="94"/>
       <c r="BI2" s="50"/>
     </row>
     <row r="3" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P3" s="52"/>
       <c r="Q3" s="52"/>
@@ -6881,7 +6989,7 @@
       <c r="AL3" s="32"/>
       <c r="AP3" s="47"/>
       <c r="BC3" s="48"/>
-      <c r="BH3" s="93"/>
+      <c r="BH3" s="94"/>
       <c r="BI3" s="53"/>
       <c r="BK3" s="54"/>
       <c r="BL3" s="54"/>
@@ -6893,24 +7001,24 @@
       <c r="BR3" s="55"/>
       <c r="BT3" s="54"/>
       <c r="BU3" s="54"/>
-      <c r="CM3" s="96"/>
-      <c r="CN3" s="96"/>
+      <c r="CM3" s="97"/>
+      <c r="CN3" s="97"/>
     </row>
     <row r="4" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A4" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="B4" s="40" t="s">
+        <v>180</v>
+      </c>
+      <c r="D4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F4" t="s">
         <v>183</v>
-      </c>
-      <c r="B4" s="40" t="s">
-        <v>184</v>
-      </c>
-      <c r="D4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E4" t="s">
-        <v>186</v>
-      </c>
-      <c r="F4" t="s">
-        <v>187</v>
       </c>
       <c r="P4" s="52"/>
       <c r="Q4" s="52"/>
@@ -6927,7 +7035,7 @@
       <c r="AP4" s="47"/>
       <c r="BC4" s="48"/>
       <c r="BF4" s="56"/>
-      <c r="BH4" s="93"/>
+      <c r="BH4" s="94"/>
       <c r="BI4" s="50"/>
       <c r="CQ4" s="56"/>
       <c r="CR4" s="56"/>
@@ -6936,19 +7044,19 @@
     </row>
     <row r="5" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A5" s="39" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F5" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P5" s="52"/>
       <c r="Q5" s="52"/>
@@ -6965,7 +7073,7 @@
       <c r="AP5" s="47"/>
       <c r="BC5" s="48"/>
       <c r="BF5" s="51"/>
-      <c r="BH5" s="93"/>
+      <c r="BH5" s="94"/>
       <c r="BI5" s="53"/>
       <c r="BJ5" s="57"/>
       <c r="BK5" s="54"/>
@@ -6985,19 +7093,19 @@
     </row>
     <row r="6" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A6" s="39" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D6" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E6" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P6" s="52"/>
       <c r="Q6" s="52"/>
@@ -7013,7 +7121,7 @@
       <c r="AJ6" s="32"/>
       <c r="AP6" s="47"/>
       <c r="BC6" s="48"/>
-      <c r="BH6" s="93"/>
+      <c r="BH6" s="94"/>
       <c r="BI6" s="50"/>
       <c r="BK6" s="61"/>
       <c r="BL6" s="61"/>
@@ -7032,19 +7140,19 @@
     </row>
     <row r="7" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A7" s="39" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="D7" t="s">
+        <v>192</v>
+      </c>
+      <c r="E7" t="s">
+        <v>193</v>
+      </c>
+      <c r="F7" t="s">
         <v>194</v>
-      </c>
-      <c r="B7" s="40" t="s">
-        <v>195</v>
-      </c>
-      <c r="D7" t="s">
-        <v>196</v>
-      </c>
-      <c r="E7" t="s">
-        <v>197</v>
-      </c>
-      <c r="F7" t="s">
-        <v>198</v>
       </c>
       <c r="P7" s="66"/>
       <c r="Q7" s="66"/>
@@ -7060,7 +7168,7 @@
       <c r="AJ7" s="32"/>
       <c r="AP7" s="47"/>
       <c r="BC7" s="48"/>
-      <c r="BH7" s="93"/>
+      <c r="BH7" s="94"/>
       <c r="BI7" s="53"/>
       <c r="BK7" s="54"/>
       <c r="BL7" s="54"/>
@@ -7079,19 +7187,19 @@
     </row>
     <row r="8" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A8" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="B8" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="D8" t="s">
+        <v>197</v>
+      </c>
+      <c r="E8" t="s">
+        <v>198</v>
+      </c>
+      <c r="F8" t="s">
         <v>199</v>
-      </c>
-      <c r="B8" s="40" t="s">
-        <v>200</v>
-      </c>
-      <c r="D8" t="s">
-        <v>201</v>
-      </c>
-      <c r="E8" t="s">
-        <v>202</v>
-      </c>
-      <c r="F8" t="s">
-        <v>203</v>
       </c>
       <c r="P8" s="68"/>
       <c r="Q8" s="69"/>
@@ -7107,7 +7215,7 @@
       <c r="AJ8" s="32"/>
       <c r="AP8" s="47"/>
       <c r="BC8" s="48"/>
-      <c r="BH8" s="93"/>
+      <c r="BH8" s="94"/>
       <c r="BI8" s="50"/>
       <c r="CQ8" s="63"/>
       <c r="CR8" s="64"/>
@@ -7116,19 +7224,19 @@
     </row>
     <row r="9" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A9" s="39" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D9" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E9" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F9" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P9" s="52"/>
       <c r="Q9" s="52"/>
@@ -7144,7 +7252,7 @@
       <c r="AJ9" s="32"/>
       <c r="AP9" s="47"/>
       <c r="BC9" s="48"/>
-      <c r="BH9" s="93"/>
+      <c r="BH9" s="94"/>
       <c r="BI9" s="53"/>
       <c r="BJ9" s="57"/>
       <c r="BK9" s="54"/>
@@ -7160,19 +7268,19 @@
     </row>
     <row r="10" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A10" s="39" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D10" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E10" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F10" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P10" s="52"/>
       <c r="Q10" s="52"/>
@@ -7188,24 +7296,24 @@
       <c r="AJ10" s="32"/>
       <c r="AP10" s="47"/>
       <c r="BC10" s="48"/>
-      <c r="BH10" s="93"/>
+      <c r="BH10" s="94"/>
       <c r="BI10" s="50"/>
     </row>
     <row r="11" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A11" s="71" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B11" s="72" t="s">
+        <v>203</v>
+      </c>
+      <c r="D11" t="s">
+        <v>206</v>
+      </c>
+      <c r="E11" t="s">
+        <v>206</v>
+      </c>
+      <c r="F11" t="s">
         <v>207</v>
-      </c>
-      <c r="D11" t="s">
-        <v>210</v>
-      </c>
-      <c r="E11" t="s">
-        <v>210</v>
-      </c>
-      <c r="F11" t="s">
-        <v>211</v>
       </c>
       <c r="P11" s="73"/>
       <c r="Q11" s="73"/>
@@ -7221,7 +7329,7 @@
       <c r="AJ11" s="32"/>
       <c r="AP11" s="47"/>
       <c r="BC11" s="48"/>
-      <c r="BH11" s="94"/>
+      <c r="BH11" s="95"/>
       <c r="BI11" s="75"/>
       <c r="BJ11" s="76"/>
       <c r="BK11" s="77"/>
@@ -7237,19 +7345,19 @@
     </row>
     <row r="12" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D12" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E12" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F12" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="Q12" s="52"/>
       <c r="R12" s="52"/>
@@ -7264,24 +7372,24 @@
       <c r="AJ12" s="32"/>
       <c r="AP12" s="47"/>
       <c r="BC12" s="48"/>
-      <c r="BH12" s="93"/>
+      <c r="BH12" s="94"/>
       <c r="BI12" s="50"/>
     </row>
     <row r="13" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A13" s="39" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B13" s="40" t="s">
+        <v>209</v>
+      </c>
+      <c r="D13" t="s">
+        <v>212</v>
+      </c>
+      <c r="E13" t="s">
         <v>213</v>
       </c>
-      <c r="D13" t="s">
-        <v>216</v>
-      </c>
-      <c r="E13" t="s">
-        <v>217</v>
-      </c>
       <c r="F13" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P13" s="66"/>
       <c r="Q13" s="66"/>
@@ -7297,7 +7405,7 @@
       <c r="AJ13" s="32"/>
       <c r="AP13" s="47"/>
       <c r="BC13" s="48"/>
-      <c r="BH13" s="93"/>
+      <c r="BH13" s="94"/>
       <c r="BI13" s="53"/>
       <c r="BK13" s="54"/>
       <c r="BL13" s="54"/>
@@ -7312,19 +7420,19 @@
     </row>
     <row r="14" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B14" s="40" t="s">
+        <v>209</v>
+      </c>
+      <c r="D14" t="s">
         <v>213</v>
       </c>
-      <c r="D14" t="s">
-        <v>217</v>
-      </c>
       <c r="E14" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="F14" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P14" s="52"/>
       <c r="Q14" s="52"/>
@@ -7339,24 +7447,24 @@
       <c r="AG14" s="46"/>
       <c r="AP14" s="47"/>
       <c r="BC14" s="48"/>
-      <c r="BH14" s="93"/>
+      <c r="BH14" s="94"/>
       <c r="BI14" s="50"/>
     </row>
     <row r="15" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A15" s="39" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D15" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E15" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F15" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P15" s="78"/>
       <c r="Q15" s="78"/>
@@ -7370,7 +7478,7 @@
       <c r="AF15" s="45"/>
       <c r="AG15" s="46"/>
       <c r="AP15" s="47"/>
-      <c r="BH15" s="93"/>
+      <c r="BH15" s="94"/>
       <c r="BI15" s="53"/>
       <c r="BK15" s="54"/>
       <c r="BL15" s="54"/>
@@ -7385,19 +7493,19 @@
     </row>
     <row r="16" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A16" s="39" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D16" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E16" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F16" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P16" s="78"/>
       <c r="Q16" s="78"/>
@@ -7411,24 +7519,24 @@
       <c r="AF16" s="45"/>
       <c r="AG16" s="46"/>
       <c r="AP16" s="47"/>
-      <c r="BH16" s="93"/>
+      <c r="BH16" s="94"/>
       <c r="BI16" s="50"/>
     </row>
     <row r="17" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A17" s="80" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B17" s="81" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D17" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E17" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F17" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P17" s="66"/>
       <c r="Q17" s="66"/>
@@ -7442,7 +7550,7 @@
       <c r="AF17" s="45"/>
       <c r="AG17" s="46"/>
       <c r="AP17" s="47"/>
-      <c r="BH17" s="93"/>
+      <c r="BH17" s="94"/>
       <c r="BI17" s="53"/>
       <c r="BK17" s="54"/>
       <c r="BL17" s="54"/>
@@ -7457,19 +7565,19 @@
     </row>
     <row r="18" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A18" s="39" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D18" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E18" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F18" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P18" s="52"/>
       <c r="Q18" s="52"/>
@@ -7483,20 +7591,20 @@
       <c r="AF18" s="82"/>
       <c r="AG18" s="83"/>
       <c r="AP18" s="47"/>
-      <c r="BH18" s="93"/>
+      <c r="BH18" s="94"/>
       <c r="BI18" s="50"/>
     </row>
     <row r="19" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A19" s="84"/>
       <c r="B19" s="84"/>
       <c r="D19" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E19" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F19" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P19" s="78"/>
       <c r="Q19" s="52"/>
@@ -7508,20 +7616,20 @@
       <c r="X19"/>
       <c r="AA19" s="32"/>
       <c r="AP19" s="47"/>
-      <c r="BH19" s="93"/>
+      <c r="BH19" s="94"/>
       <c r="BI19" s="53"/>
     </row>
     <row r="20" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A20" s="84"/>
       <c r="B20" s="84"/>
       <c r="D20" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E20" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F20" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P20" s="52"/>
       <c r="Q20" s="52"/>
@@ -7533,7 +7641,7 @@
       <c r="X20"/>
       <c r="AA20" s="32"/>
       <c r="AP20" s="47"/>
-      <c r="BH20" s="93"/>
+      <c r="BH20" s="94"/>
       <c r="BI20" s="50"/>
       <c r="BK20" s="54"/>
       <c r="BL20" s="54"/>
@@ -7550,13 +7658,13 @@
       <c r="A21" s="84"/>
       <c r="B21" s="84"/>
       <c r="D21" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E21" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F21" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P21" s="52"/>
       <c r="Q21" s="52"/>
@@ -7568,7 +7676,7 @@
       <c r="X21"/>
       <c r="AA21" s="32"/>
       <c r="AP21" s="47"/>
-      <c r="BH21" s="94"/>
+      <c r="BH21" s="95"/>
       <c r="BI21" s="75"/>
       <c r="BJ21" s="76"/>
       <c r="BK21" s="77"/>
@@ -7586,13 +7694,13 @@
       <c r="A22" s="84"/>
       <c r="B22" s="84"/>
       <c r="D22" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E22" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F22" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P22" s="52"/>
       <c r="Q22" s="52"/>
@@ -7605,20 +7713,20 @@
       <c r="AA22" s="32"/>
       <c r="AF22" s="85"/>
       <c r="AG22" s="86"/>
-      <c r="BH22" s="93"/>
+      <c r="BH22" s="94"/>
       <c r="BI22" s="50"/>
     </row>
     <row r="23" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A23" s="84"/>
       <c r="B23" s="84"/>
       <c r="D23" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E23" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F23" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P23" s="66"/>
       <c r="Q23" s="66"/>
@@ -7629,7 +7737,7 @@
       <c r="V23" s="67"/>
       <c r="X23"/>
       <c r="AA23" s="32"/>
-      <c r="BH23" s="93"/>
+      <c r="BH23" s="94"/>
       <c r="BI23" s="53"/>
       <c r="BK23" s="54"/>
       <c r="BL23" s="54"/>
@@ -7646,13 +7754,13 @@
       <c r="A24" s="87"/>
       <c r="B24" s="87"/>
       <c r="D24" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E24" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F24" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P24" s="78"/>
       <c r="Q24" s="78"/>
@@ -7672,20 +7780,20 @@
       <c r="AW24" s="35"/>
       <c r="AX24" s="35"/>
       <c r="AY24" s="35"/>
-      <c r="BH24" s="93"/>
+      <c r="BH24" s="94"/>
       <c r="BI24" s="50"/>
     </row>
     <row r="25" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A25" s="87"/>
       <c r="B25" s="87"/>
       <c r="D25" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E25" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F25" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P25" s="52"/>
       <c r="Q25" s="52"/>
@@ -7697,7 +7805,7 @@
       <c r="X25"/>
       <c r="AA25" s="32"/>
       <c r="AP25" s="47"/>
-      <c r="BH25" s="93"/>
+      <c r="BH25" s="94"/>
       <c r="BI25" s="53"/>
       <c r="BK25" s="54"/>
       <c r="BL25" s="54"/>
@@ -7714,13 +7822,13 @@
       <c r="A26" s="87"/>
       <c r="B26" s="87"/>
       <c r="D26" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E26" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F26" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P26" s="78"/>
       <c r="Q26" s="78"/>
@@ -7732,20 +7840,20 @@
       <c r="X26"/>
       <c r="AA26" s="32"/>
       <c r="AP26" s="47"/>
-      <c r="BH26" s="93"/>
+      <c r="BH26" s="94"/>
       <c r="BI26" s="50"/>
     </row>
     <row r="27" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A27" s="87"/>
       <c r="B27" s="87"/>
       <c r="D27" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E27" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F27" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P27" s="78"/>
       <c r="Q27" s="78"/>
@@ -7757,7 +7865,7 @@
       <c r="X27"/>
       <c r="AA27" s="32"/>
       <c r="AP27" s="47"/>
-      <c r="BH27" s="93"/>
+      <c r="BH27" s="94"/>
       <c r="BI27" s="53"/>
       <c r="BK27" s="54"/>
       <c r="BL27" s="54"/>
@@ -7774,13 +7882,13 @@
       <c r="A28" s="87"/>
       <c r="B28" s="87"/>
       <c r="D28" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E28" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F28" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P28" s="52"/>
       <c r="Q28" s="88"/>
@@ -7792,7 +7900,7 @@
       <c r="X28"/>
       <c r="AA28" s="32"/>
       <c r="AP28" s="47"/>
-      <c r="BH28" s="93"/>
+      <c r="BH28" s="94"/>
       <c r="BI28" s="50"/>
       <c r="BK28" s="61"/>
       <c r="BL28" s="61"/>
@@ -7807,13 +7915,13 @@
       <c r="A29" s="87"/>
       <c r="B29" s="87"/>
       <c r="D29" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E29" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F29" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P29" s="52"/>
       <c r="Q29" s="52"/>
@@ -7825,7 +7933,7 @@
       <c r="X29"/>
       <c r="AA29" s="32"/>
       <c r="AP29" s="47"/>
-      <c r="BH29" s="93"/>
+      <c r="BH29" s="94"/>
       <c r="BI29" s="53"/>
       <c r="BJ29" s="57"/>
       <c r="BK29" s="54"/>
@@ -7843,13 +7951,13 @@
       <c r="A30" s="87"/>
       <c r="B30" s="87"/>
       <c r="D30" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E30" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F30" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P30" s="78"/>
       <c r="Q30" s="78"/>
@@ -7860,20 +7968,20 @@
       <c r="V30" s="79"/>
       <c r="X30"/>
       <c r="AA30" s="32"/>
-      <c r="BH30" s="93"/>
+      <c r="BH30" s="94"/>
       <c r="BI30" s="50"/>
     </row>
     <row r="31" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A31" s="87"/>
       <c r="B31" s="87"/>
       <c r="D31" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E31" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F31" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P31" s="52"/>
       <c r="Q31" s="52"/>
@@ -7884,7 +7992,7 @@
       <c r="V31" s="44"/>
       <c r="X31"/>
       <c r="AA31" s="32"/>
-      <c r="BH31" s="94"/>
+      <c r="BH31" s="95"/>
       <c r="BI31" s="75"/>
       <c r="BK31" s="77"/>
       <c r="BL31" s="77"/>
@@ -7901,13 +8009,13 @@
       <c r="A32" s="87"/>
       <c r="B32" s="87"/>
       <c r="D32" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E32" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F32" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P32" s="52"/>
       <c r="Q32" s="52"/>
@@ -7924,18 +8032,18 @@
       <c r="AW32"/>
       <c r="AX32"/>
       <c r="AY32"/>
-      <c r="BH32" s="93"/>
+      <c r="BH32" s="94"/>
       <c r="BI32" s="50"/>
     </row>
     <row r="33" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D33" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E33" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F33" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P33" s="78"/>
       <c r="Q33" s="78"/>
@@ -7952,7 +8060,7 @@
       <c r="AW33"/>
       <c r="AX33"/>
       <c r="AY33"/>
-      <c r="BH33" s="93"/>
+      <c r="BH33" s="94"/>
       <c r="BI33" s="53"/>
       <c r="BK33" s="54"/>
       <c r="BL33" s="54"/>
@@ -7967,13 +8075,13 @@
     </row>
     <row r="34" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D34" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E34" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F34" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P34" s="52"/>
       <c r="Q34" s="52"/>
@@ -7990,18 +8098,18 @@
       <c r="AW34"/>
       <c r="AX34"/>
       <c r="AY34"/>
-      <c r="BH34" s="93"/>
+      <c r="BH34" s="94"/>
       <c r="BI34" s="50"/>
     </row>
     <row r="35" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D35" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="E35" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F35" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P35" s="78"/>
       <c r="Q35" s="78"/>
@@ -8018,7 +8126,7 @@
       <c r="AW35"/>
       <c r="AX35"/>
       <c r="AY35"/>
-      <c r="BH35" s="93"/>
+      <c r="BH35" s="94"/>
       <c r="BI35" s="53"/>
       <c r="BJ35" s="57"/>
       <c r="BK35" s="54"/>
@@ -8034,13 +8142,13 @@
     </row>
     <row r="36" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D36" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E36" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F36" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P36" s="78"/>
       <c r="Q36" s="78"/>
@@ -8057,18 +8165,18 @@
       <c r="AW36"/>
       <c r="AX36"/>
       <c r="AY36"/>
-      <c r="BH36" s="93"/>
+      <c r="BH36" s="94"/>
       <c r="BI36" s="50"/>
     </row>
     <row r="37" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D37" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="E37" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F37" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P37" s="78"/>
       <c r="Q37" s="78"/>
@@ -8085,7 +8193,7 @@
       <c r="AW37"/>
       <c r="AX37"/>
       <c r="AY37"/>
-      <c r="BH37" s="93"/>
+      <c r="BH37" s="94"/>
       <c r="BI37" s="53"/>
       <c r="BK37" s="54"/>
       <c r="BL37" s="54"/>
@@ -8100,13 +8208,13 @@
     </row>
     <row r="38" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D38" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E38" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F38" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P38" s="52"/>
       <c r="Q38" s="52"/>
@@ -8123,18 +8231,18 @@
       <c r="AW38"/>
       <c r="AX38"/>
       <c r="AY38"/>
-      <c r="BH38" s="93"/>
+      <c r="BH38" s="94"/>
       <c r="BI38" s="50"/>
     </row>
     <row r="39" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D39" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E39" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F39" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="S39" s="44"/>
       <c r="T39" s="44"/>
@@ -8142,7 +8250,7 @@
       <c r="V39" s="44"/>
       <c r="X39"/>
       <c r="AA39" s="32"/>
-      <c r="BH39" s="93"/>
+      <c r="BH39" s="94"/>
       <c r="BI39" s="53"/>
       <c r="BJ39" s="57"/>
       <c r="BK39" s="54"/>
@@ -8158,13 +8266,13 @@
     </row>
     <row r="40" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D40" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E40" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F40" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P40" s="52"/>
       <c r="Q40" s="52"/>
@@ -8175,25 +8283,25 @@
       <c r="V40" s="44"/>
       <c r="X40"/>
       <c r="AA40" s="32"/>
-      <c r="BH40" s="93"/>
+      <c r="BH40" s="94"/>
       <c r="BI40" s="50"/>
     </row>
     <row r="41" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D41" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E41" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="F41" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="S41" s="44"/>
       <c r="T41" s="44"/>
       <c r="U41"/>
       <c r="X41"/>
       <c r="AA41" s="32"/>
-      <c r="BH41" s="94"/>
+      <c r="BH41" s="95"/>
       <c r="BI41" s="75"/>
       <c r="BK41" s="77"/>
       <c r="BL41" s="77"/>
@@ -8208,13 +8316,13 @@
     </row>
     <row r="42" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D42" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="E42" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F42" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P42" s="52"/>
       <c r="Q42" s="52"/>
@@ -8225,18 +8333,18 @@
       <c r="V42" s="44"/>
       <c r="X42"/>
       <c r="AA42" s="32"/>
-      <c r="BH42" s="93"/>
+      <c r="BH42" s="94"/>
       <c r="BI42" s="50"/>
     </row>
     <row r="43" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D43" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E43" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F43" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P43" s="78"/>
       <c r="Q43" s="52"/>
@@ -8247,7 +8355,7 @@
       <c r="V43" s="44"/>
       <c r="X43"/>
       <c r="AA43" s="32"/>
-      <c r="BH43" s="93"/>
+      <c r="BH43" s="94"/>
       <c r="BI43" s="53"/>
       <c r="BJ43" s="57"/>
       <c r="BK43" s="54"/>
@@ -8263,13 +8371,13 @@
     </row>
     <row r="44" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D44" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E44" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F44" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P44" s="78"/>
       <c r="Q44" s="52"/>
@@ -8280,18 +8388,18 @@
       <c r="V44" s="44"/>
       <c r="X44"/>
       <c r="AA44" s="32"/>
-      <c r="BH44" s="93"/>
+      <c r="BH44" s="94"/>
       <c r="BI44" s="50"/>
     </row>
     <row r="45" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D45" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E45" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F45" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P45" s="78"/>
       <c r="Q45" s="52"/>
@@ -8302,7 +8410,7 @@
       <c r="V45" s="44"/>
       <c r="X45"/>
       <c r="AA45" s="32"/>
-      <c r="BH45" s="93"/>
+      <c r="BH45" s="94"/>
       <c r="BI45" s="53"/>
       <c r="BJ45" s="57"/>
       <c r="BK45" s="54"/>
@@ -8318,13 +8426,13 @@
     </row>
     <row r="46" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D46" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E46" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F46" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P46" s="78"/>
       <c r="Q46" s="78"/>
@@ -8335,18 +8443,18 @@
       <c r="V46" s="79"/>
       <c r="X46"/>
       <c r="AA46" s="32"/>
-      <c r="BH46" s="93"/>
+      <c r="BH46" s="94"/>
       <c r="BI46" s="50"/>
     </row>
     <row r="47" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D47" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E47" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F47" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P47" s="52"/>
       <c r="Q47" s="52"/>
@@ -8357,7 +8465,7 @@
       <c r="V47" s="44"/>
       <c r="X47"/>
       <c r="AA47" s="32"/>
-      <c r="BH47" s="93"/>
+      <c r="BH47" s="94"/>
       <c r="BI47" s="53"/>
       <c r="BJ47" s="57"/>
       <c r="BK47" s="54"/>
@@ -8373,13 +8481,13 @@
     </row>
     <row r="48" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D48" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E48" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F48" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P48" s="52"/>
       <c r="Q48" s="52"/>
@@ -8390,18 +8498,18 @@
       <c r="V48" s="44"/>
       <c r="X48"/>
       <c r="AA48" s="32"/>
-      <c r="BH48" s="93"/>
+      <c r="BH48" s="94"/>
       <c r="BI48" s="50"/>
     </row>
     <row r="49" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F49" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P49" s="52"/>
       <c r="Q49" s="52"/>
@@ -8412,7 +8520,7 @@
       <c r="V49" s="44"/>
       <c r="X49"/>
       <c r="AA49" s="32"/>
-      <c r="BH49" s="93"/>
+      <c r="BH49" s="94"/>
       <c r="BI49" s="53"/>
       <c r="BJ49" s="57"/>
       <c r="BK49" s="54"/>
@@ -8428,13 +8536,13 @@
     </row>
     <row r="50" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D50" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E50" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F50" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P50" s="52"/>
       <c r="Q50" s="52"/>
@@ -8445,18 +8553,18 @@
       <c r="V50" s="44"/>
       <c r="X50"/>
       <c r="AA50" s="32"/>
-      <c r="BH50" s="93"/>
+      <c r="BH50" s="94"/>
       <c r="BI50" s="50"/>
     </row>
     <row r="51" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D51" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E51" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F51" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P51" s="78"/>
       <c r="Q51" s="78"/>
@@ -8467,7 +8575,7 @@
       <c r="V51" s="79"/>
       <c r="X51"/>
       <c r="AA51" s="32"/>
-      <c r="BH51" s="94"/>
+      <c r="BH51" s="95"/>
       <c r="BI51" s="75"/>
       <c r="BJ51" s="76"/>
       <c r="BK51" s="77"/>
@@ -8483,13 +8591,13 @@
     </row>
     <row r="52" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D52" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E52" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F52" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P52" s="78"/>
       <c r="Q52" s="78"/>
@@ -8505,13 +8613,13 @@
     </row>
     <row r="53" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D53" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E53" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="F53" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P53" s="78"/>
       <c r="Q53" s="78"/>
@@ -8525,13 +8633,13 @@
     </row>
     <row r="54" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D54" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E54" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="F54" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P54" s="52"/>
       <c r="Q54" s="52"/>
@@ -8545,13 +8653,13 @@
     </row>
     <row r="55" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D55" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E55" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F55" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P55" s="78"/>
       <c r="Q55" s="78"/>
@@ -8566,13 +8674,13 @@
     </row>
     <row r="56" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D56" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E56" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F56" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P56" s="52"/>
       <c r="Q56" s="52"/>
@@ -8587,13 +8695,13 @@
     </row>
     <row r="57" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D57" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E57" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="F57" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="Q57" s="52"/>
       <c r="R57" s="52"/>
@@ -8607,13 +8715,13 @@
     </row>
     <row r="58" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D58" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E58" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="F58" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P58" s="78"/>
       <c r="Q58" s="78"/>
@@ -8628,13 +8736,13 @@
     </row>
     <row r="59" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D59" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E59" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F59" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P59" s="52"/>
       <c r="Q59" s="52"/>
@@ -8649,13 +8757,13 @@
     </row>
     <row r="60" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D60" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E60" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="F60" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P60" s="78"/>
       <c r="Q60" s="78"/>
@@ -8670,13 +8778,13 @@
     </row>
     <row r="61" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D61" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E61" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="F61" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P61" s="78"/>
       <c r="Q61" s="78"/>
@@ -8691,13 +8799,13 @@
     </row>
     <row r="62" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D62" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E62" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F62" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P62" s="52"/>
       <c r="Q62" s="52"/>
@@ -8711,13 +8819,13 @@
     </row>
     <row r="63" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D63" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E63" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F63" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P63" s="52"/>
       <c r="Q63" s="52"/>
@@ -8731,13 +8839,13 @@
     </row>
     <row r="64" spans="4:73" x14ac:dyDescent="0.25">
       <c r="D64" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E64" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F64" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P64" s="52"/>
       <c r="Q64" s="52"/>
@@ -8751,13 +8859,13 @@
     </row>
     <row r="65" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D65" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E65" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F65" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P65" s="78"/>
       <c r="Q65" s="78"/>
@@ -8771,13 +8879,13 @@
     </row>
     <row r="66" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D66" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E66" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F66" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P66" s="78"/>
       <c r="Q66" s="78"/>
@@ -8791,13 +8899,13 @@
     </row>
     <row r="67" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D67" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E67" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F67" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P67" s="52"/>
       <c r="Q67" s="52"/>
@@ -8811,13 +8919,13 @@
     </row>
     <row r="68" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D68" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E68" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F68" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P68" s="78"/>
       <c r="Q68" s="78"/>
@@ -8831,13 +8939,13 @@
     </row>
     <row r="69" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D69" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E69" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F69" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P69" s="84"/>
       <c r="Q69" s="52"/>
@@ -8851,13 +8959,13 @@
     </row>
     <row r="70" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D70" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E70" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F70" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P70" s="78"/>
       <c r="Q70" s="78"/>
@@ -8871,13 +8979,13 @@
     </row>
     <row r="71" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D71" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E71" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F71" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P71" s="78"/>
       <c r="Q71" s="78"/>
@@ -8891,13 +8999,13 @@
     </row>
     <row r="72" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D72" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E72" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F72" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="U72"/>
       <c r="X72"/>
@@ -8905,13 +9013,13 @@
     </row>
     <row r="73" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D73" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E73" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F73" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P73" s="52"/>
       <c r="R73" s="52"/>
@@ -8924,13 +9032,13 @@
     </row>
     <row r="74" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D74" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="E74" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F74" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Q74" s="52"/>
       <c r="R74" s="52"/>
@@ -8943,13 +9051,13 @@
     </row>
     <row r="75" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D75" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="E75" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F75" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="S75" s="44"/>
       <c r="T75" s="44"/>
@@ -8959,13 +9067,13 @@
     </row>
     <row r="76" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D76" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E76" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F76" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P76" s="78"/>
       <c r="Q76" s="78"/>
@@ -8979,13 +9087,13 @@
     </row>
     <row r="77" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D77" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E77" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F77" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="P77" s="52"/>
       <c r="Q77" s="52"/>
@@ -8999,13 +9107,13 @@
     </row>
     <row r="78" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D78" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E78" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F78" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P78" s="78"/>
       <c r="Q78" s="78"/>
@@ -9019,13 +9127,13 @@
     </row>
     <row r="79" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D79" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E79" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F79" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P79" s="78"/>
       <c r="Q79" s="78"/>
@@ -9039,13 +9147,13 @@
     </row>
     <row r="80" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D80" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E80" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F80" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P80" s="52"/>
       <c r="Q80" s="52"/>
@@ -9059,13 +9167,13 @@
     </row>
     <row r="81" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D81" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="E81" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="F81" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P81" s="78"/>
       <c r="Q81" s="78"/>
@@ -9079,13 +9187,13 @@
     </row>
     <row r="82" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D82" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E82" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F82" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="Q82" s="52"/>
       <c r="R82" s="52"/>
@@ -9098,13 +9206,13 @@
     </row>
     <row r="83" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D83" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E83" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F83" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P83" s="52"/>
       <c r="Q83" s="52"/>
@@ -9118,13 +9226,13 @@
     </row>
     <row r="84" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D84" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E84" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F84" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P84" s="78"/>
       <c r="Q84" s="78"/>
@@ -9138,13 +9246,13 @@
     </row>
     <row r="85" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D85" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E85" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="F85" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P85" s="78"/>
       <c r="Q85" s="78"/>
@@ -9158,13 +9266,13 @@
     </row>
     <row r="86" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D86" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="E86" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F86" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="Q86" s="78"/>
       <c r="R86" s="78"/>
@@ -9177,13 +9285,13 @@
     </row>
     <row r="87" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D87" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E87" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F87" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P87" s="78"/>
       <c r="R87" s="78"/>
@@ -9196,13 +9304,13 @@
     </row>
     <row r="88" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D88" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E88" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F88" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="P88" s="78"/>
       <c r="Q88" s="78"/>
@@ -9216,13 +9324,13 @@
     </row>
     <row r="89" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D89" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="E89" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F89" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P89" s="78"/>
       <c r="Q89" s="78"/>
@@ -9236,13 +9344,13 @@
     </row>
     <row r="90" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D90" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E90" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F90" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Q90" s="52"/>
       <c r="R90" s="52"/>
@@ -9255,13 +9363,13 @@
     </row>
     <row r="91" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D91" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E91" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F91" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P91" s="52"/>
       <c r="Q91" s="52"/>
@@ -9275,13 +9383,13 @@
     </row>
     <row r="92" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D92" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E92" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F92" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P92" s="66"/>
       <c r="S92" s="44"/>
@@ -9292,13 +9400,13 @@
     </row>
     <row r="93" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D93" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E93" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F93" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P93" s="78"/>
       <c r="Q93" s="52"/>
@@ -9312,13 +9420,13 @@
     </row>
     <row r="94" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D94" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E94" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F94" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P94" s="78"/>
       <c r="Q94" s="78"/>
@@ -9332,13 +9440,13 @@
     </row>
     <row r="95" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D95" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E95" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F95" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="S95" s="44"/>
       <c r="V95" s="44"/>
@@ -9347,13 +9455,13 @@
     </row>
     <row r="96" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D96" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E96" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="F96" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P96" s="78"/>
       <c r="Q96" s="78"/>
@@ -9367,13 +9475,13 @@
     </row>
     <row r="97" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D97" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="E97" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="F97" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Q97" s="52"/>
       <c r="R97" s="52"/>
@@ -9386,13 +9494,13 @@
     </row>
     <row r="98" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D98" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E98" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F98" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P98" s="78"/>
       <c r="Q98" s="52"/>
@@ -9405,13 +9513,13 @@
     </row>
     <row r="99" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D99" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E99" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F99" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P99" s="78"/>
       <c r="Q99" s="52"/>
@@ -9425,13 +9533,13 @@
     </row>
     <row r="100" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D100" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="E100" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="F100" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P100" s="52"/>
       <c r="Q100" s="52"/>
@@ -9445,13 +9553,13 @@
     </row>
     <row r="101" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D101" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E101" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F101" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P101" s="78"/>
       <c r="Q101" s="78"/>
@@ -9465,13 +9573,13 @@
     </row>
     <row r="102" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D102" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E102" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F102" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="P102" s="52"/>
       <c r="Q102" s="52"/>
@@ -9485,13 +9593,13 @@
     </row>
     <row r="103" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D103" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E103" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F103" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P103" s="78"/>
       <c r="Q103" s="78"/>
@@ -9505,13 +9613,13 @@
     </row>
     <row r="104" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D104" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E104" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F104" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P104" s="78"/>
       <c r="Q104" s="78"/>
@@ -9525,13 +9633,13 @@
     </row>
     <row r="105" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D105" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E105" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F105" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P105" s="78"/>
       <c r="Q105" s="78"/>
@@ -9545,13 +9653,13 @@
     </row>
     <row r="106" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D106" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E106" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="F106" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="S106" s="44"/>
       <c r="V106" s="44"/>
@@ -9560,13 +9668,13 @@
     </row>
     <row r="107" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D107" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E107" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F107" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P107" s="52"/>
       <c r="Q107" s="52"/>
@@ -9580,13 +9688,13 @@
     </row>
     <row r="108" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D108" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="E108" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F108" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P108" s="78"/>
       <c r="R108" s="78"/>
@@ -9599,13 +9707,13 @@
     </row>
     <row r="109" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D109" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E109" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F109" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="T109" s="44"/>
       <c r="U109" s="44"/>
@@ -9615,13 +9723,13 @@
     </row>
     <row r="110" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D110" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E110" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F110" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="T110" s="44"/>
       <c r="U110" s="44"/>
@@ -9631,13 +9739,13 @@
     </row>
     <row r="111" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D111" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="E111" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F111" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P111" s="78"/>
       <c r="Q111" s="78"/>
@@ -9651,13 +9759,13 @@
     </row>
     <row r="112" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D112" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E112" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="F112" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P112" s="78"/>
       <c r="Q112" s="78"/>
@@ -9671,13 +9779,13 @@
     </row>
     <row r="113" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D113" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E113" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F113" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P113" s="78"/>
       <c r="Q113" s="78"/>
@@ -9691,13 +9799,13 @@
     </row>
     <row r="114" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D114" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E114" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F114" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="Q114" s="52"/>
       <c r="R114" s="52"/>
@@ -9710,13 +9818,13 @@
     </row>
     <row r="115" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D115" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E115" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F115" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P115" s="52"/>
       <c r="Q115" s="52"/>
@@ -9730,13 +9838,13 @@
     </row>
     <row r="116" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D116" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E116" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F116" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="Q116" s="52"/>
       <c r="R116" s="52"/>
@@ -9749,13 +9857,13 @@
     </row>
     <row r="117" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D117" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E117" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F117" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P117" s="52"/>
       <c r="Q117" s="52"/>
@@ -9769,13 +9877,13 @@
     </row>
     <row r="118" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D118" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E118" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="F118" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P118" s="52"/>
       <c r="Q118" s="52"/>
@@ -9789,13 +9897,13 @@
     </row>
     <row r="119" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D119" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E119" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="F119" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P119" s="52"/>
       <c r="Q119" s="52"/>
@@ -9809,13 +9917,13 @@
     </row>
     <row r="120" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D120" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E120" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="F120" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P120" s="78"/>
       <c r="Q120" s="78"/>
@@ -9829,13 +9937,13 @@
     </row>
     <row r="121" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D121" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E121" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="F121" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P121" s="52"/>
       <c r="Q121" s="52"/>
@@ -9849,13 +9957,13 @@
     </row>
     <row r="122" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D122" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E122" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="F122" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P122" s="78"/>
       <c r="Q122" s="78"/>
@@ -9869,13 +9977,13 @@
     </row>
     <row r="123" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D123" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E123" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F123" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P123" s="78"/>
       <c r="Q123" s="78"/>
@@ -9889,13 +9997,13 @@
     </row>
     <row r="124" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D124" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E124" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F124" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P124" s="78"/>
       <c r="Q124" s="78"/>
@@ -9909,13 +10017,13 @@
     </row>
     <row r="125" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D125" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E125" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="F125" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P125" s="78"/>
       <c r="Q125" s="78"/>
@@ -9929,13 +10037,13 @@
     </row>
     <row r="126" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D126" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E126" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="F126" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P126" s="78"/>
       <c r="Q126" s="78"/>
@@ -9949,13 +10057,13 @@
     </row>
     <row r="127" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D127" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E127" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="F127" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P127" s="52"/>
       <c r="Q127" s="52"/>
@@ -9969,13 +10077,13 @@
     </row>
     <row r="128" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D128" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="E128" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="F128" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P128" s="78"/>
       <c r="Q128" s="78"/>
@@ -9989,13 +10097,13 @@
     </row>
     <row r="129" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D129" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E129" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="F129" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="V129" s="44"/>
       <c r="X129"/>
@@ -10003,13 +10111,13 @@
     </row>
     <row r="130" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D130" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E130" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="F130" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P130" s="78"/>
       <c r="Q130" s="78"/>
@@ -10023,13 +10131,13 @@
     </row>
     <row r="131" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D131" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="E131" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F131" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P131" s="78"/>
       <c r="Q131" s="52"/>
@@ -10043,13 +10151,13 @@
     </row>
     <row r="132" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D132" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E132" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="F132" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P132" s="52"/>
       <c r="Q132" s="52"/>
@@ -10063,13 +10171,13 @@
     </row>
     <row r="133" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D133" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E133" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F133" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P133" s="52"/>
       <c r="Q133" s="52"/>
@@ -10082,13 +10190,13 @@
     </row>
     <row r="134" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D134" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E134" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="F134" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P134" s="78"/>
       <c r="Q134" s="78"/>
@@ -10102,13 +10210,13 @@
     </row>
     <row r="135" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D135" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E135" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F135" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P135" s="52"/>
       <c r="Q135" s="52"/>
@@ -10122,13 +10230,13 @@
     </row>
     <row r="136" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D136" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E136" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="F136" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P136" s="78"/>
       <c r="Q136" s="78"/>
@@ -10142,13 +10250,13 @@
     </row>
     <row r="137" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D137" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E137" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="F137" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P137" s="52"/>
       <c r="Q137" s="52"/>
@@ -10162,13 +10270,13 @@
     </row>
     <row r="138" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D138" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="E138" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F138" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P138" s="52"/>
       <c r="Q138" s="52"/>
@@ -10182,13 +10290,13 @@
     </row>
     <row r="139" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D139" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E139" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="F139" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P139" s="52"/>
       <c r="Q139" s="52"/>
@@ -10202,13 +10310,13 @@
     </row>
     <row r="140" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D140" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E140" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="F140" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P140" s="78"/>
       <c r="Q140" s="52"/>
@@ -10222,13 +10330,13 @@
     </row>
     <row r="141" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D141" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E141" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F141" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P141" s="52"/>
       <c r="Q141" s="52"/>
@@ -10242,13 +10350,13 @@
     </row>
     <row r="142" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D142" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="E142" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="F142" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P142" s="52"/>
       <c r="Q142" s="52"/>
@@ -10262,13 +10370,13 @@
     </row>
     <row r="143" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D143" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E143" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F143" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P143" s="52"/>
       <c r="Q143" s="52"/>
@@ -10282,13 +10390,13 @@
     </row>
     <row r="144" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D144" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E144" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F144" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P144" s="52"/>
       <c r="Q144" s="52"/>
@@ -10302,13 +10410,13 @@
     </row>
     <row r="145" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D145" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E145" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="F145" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P145" s="78"/>
       <c r="Q145" s="78"/>
@@ -10322,13 +10430,13 @@
     </row>
     <row r="146" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D146" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="E146" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="F146" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P146" s="52"/>
       <c r="Q146" s="52"/>
@@ -10342,13 +10450,13 @@
     </row>
     <row r="147" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D147" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="E147" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="F147" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="S147"/>
       <c r="T147"/>
@@ -10359,13 +10467,13 @@
     </row>
     <row r="148" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D148" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E148" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F148" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P148" s="78"/>
       <c r="Q148" s="78"/>
@@ -10379,13 +10487,13 @@
     </row>
     <row r="149" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D149" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E149" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F149" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P149" s="52"/>
       <c r="Q149" s="52"/>
@@ -10399,13 +10507,13 @@
     </row>
     <row r="150" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D150" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E150" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F150" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P150" s="78"/>
       <c r="Q150" s="78"/>
@@ -10419,13 +10527,13 @@
     </row>
     <row r="151" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D151" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E151" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="F151" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="P151" s="78"/>
       <c r="Q151" s="78"/>
@@ -10439,13 +10547,13 @@
     </row>
     <row r="152" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D152" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="E152" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="F152" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P152" s="78"/>
       <c r="Q152" s="78"/>
@@ -10459,13 +10567,13 @@
     </row>
     <row r="153" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D153" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E153" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="F153" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P153" s="78"/>
       <c r="Q153" s="78"/>
@@ -10479,13 +10587,13 @@
     </row>
     <row r="154" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D154" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E154" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="F154" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P154" s="78"/>
       <c r="Q154" s="78"/>
@@ -10499,13 +10607,13 @@
     </row>
     <row r="155" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D155" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="E155" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="F155" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P155" s="78"/>
       <c r="Q155" s="78"/>
@@ -10519,13 +10627,13 @@
     </row>
     <row r="156" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D156" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="E156" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="F156" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P156" s="78"/>
       <c r="Q156" s="78"/>
@@ -10539,13 +10647,13 @@
     </row>
     <row r="157" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D157" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E157" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F157" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P157" s="78"/>
       <c r="Q157" s="78"/>
@@ -10559,13 +10667,13 @@
     </row>
     <row r="158" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D158" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="E158" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F158" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P158" s="52"/>
       <c r="Q158" s="52"/>
@@ -10579,13 +10687,13 @@
     </row>
     <row r="159" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D159" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="E159" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="F159" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P159" s="78"/>
       <c r="Q159" s="78"/>
@@ -10599,13 +10707,13 @@
     </row>
     <row r="160" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D160" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E160" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="F160" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P160" s="78"/>
       <c r="Q160" s="52"/>
@@ -10619,13 +10727,13 @@
     </row>
     <row r="161" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D161" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E161" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="F161" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P161" s="78"/>
       <c r="Q161" s="78"/>
@@ -10639,13 +10747,13 @@
     </row>
     <row r="162" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D162" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E162" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="F162" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P162" s="78"/>
       <c r="R162" s="78"/>
@@ -10658,13 +10766,13 @@
     </row>
     <row r="163" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D163" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="E163" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="F163" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P163" s="78"/>
       <c r="Q163" s="78"/>
@@ -10678,13 +10786,13 @@
     </row>
     <row r="164" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D164" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="E164" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="F164" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P164" s="78"/>
       <c r="Q164" s="78"/>
@@ -10698,13 +10806,13 @@
     </row>
     <row r="165" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D165" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E165" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="F165" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P165" s="78"/>
       <c r="Q165" s="78"/>
@@ -10718,13 +10826,13 @@
     </row>
     <row r="166" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D166" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E166" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="F166" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P166" s="52"/>
       <c r="Q166" s="52"/>
@@ -10738,13 +10846,13 @@
     </row>
     <row r="167" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D167" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E167" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="F167" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P167" s="78"/>
       <c r="Q167" s="78"/>
@@ -10758,13 +10866,13 @@
     </row>
     <row r="168" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D168" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E168" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="F168" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P168" s="52"/>
       <c r="Q168" s="52"/>
@@ -10778,13 +10886,13 @@
     </row>
     <row r="169" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D169" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="E169" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="F169" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P169" s="78"/>
       <c r="Q169" s="78"/>
@@ -10798,13 +10906,13 @@
     </row>
     <row r="170" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D170" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E170" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="F170" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P170" s="78"/>
       <c r="Q170" s="78"/>
@@ -10818,13 +10926,13 @@
     </row>
     <row r="171" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D171" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="E171" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="F171" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P171" s="78"/>
       <c r="Q171" s="78"/>
@@ -10838,13 +10946,13 @@
     </row>
     <row r="172" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D172" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="E172" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="F172" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P172" s="78"/>
       <c r="Q172" s="78"/>
@@ -10858,13 +10966,13 @@
     </row>
     <row r="173" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D173" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="E173" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="F173" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P173" s="52"/>
       <c r="Q173" s="52"/>
@@ -10878,13 +10986,13 @@
     </row>
     <row r="174" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D174" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E174" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="F174" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P174" s="52"/>
       <c r="Q174" s="52"/>
@@ -10898,13 +11006,13 @@
     </row>
     <row r="175" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D175" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="E175" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="F175" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P175" s="52"/>
       <c r="Q175" s="52"/>
@@ -10918,13 +11026,13 @@
     </row>
     <row r="176" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D176" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="E176" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="F176" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P176" s="78"/>
       <c r="Q176" s="78"/>
@@ -10938,13 +11046,13 @@
     </row>
     <row r="177" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D177" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E177" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="F177" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P177" s="52"/>
       <c r="Q177" s="52"/>
@@ -10958,13 +11066,13 @@
     </row>
     <row r="178" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D178" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="E178" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="F178" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P178" s="78"/>
       <c r="Q178" s="52"/>
@@ -10978,13 +11086,13 @@
     </row>
     <row r="179" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D179" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E179" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F179" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="T179" s="44"/>
       <c r="U179" s="44"/>
@@ -10994,13 +11102,13 @@
     </row>
     <row r="180" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D180" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E180" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="F180" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P180" s="52"/>
       <c r="Q180" s="52"/>
@@ -11014,13 +11122,13 @@
     </row>
     <row r="181" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D181" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E181" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="F181" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P181" s="52"/>
       <c r="Q181" s="52"/>
@@ -11034,13 +11142,13 @@
     </row>
     <row r="182" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D182" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="E182" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F182" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P182" s="78"/>
       <c r="Q182" s="78"/>
@@ -11054,13 +11162,13 @@
     </row>
     <row r="183" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D183" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="E183" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="F183" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P183" s="52"/>
       <c r="Q183" s="52"/>
@@ -11074,13 +11182,13 @@
     </row>
     <row r="184" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D184" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="E184" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="F184" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P184" s="78"/>
       <c r="Q184" s="78"/>
@@ -11094,13 +11202,13 @@
     </row>
     <row r="185" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D185" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="E185" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="F185" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P185" s="52"/>
       <c r="Q185" s="52"/>
@@ -11114,13 +11222,13 @@
     </row>
     <row r="186" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D186" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E186" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="F186" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P186" s="78"/>
       <c r="Q186" s="78"/>
@@ -11134,13 +11242,13 @@
     </row>
     <row r="187" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D187" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="E187" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F187" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P187" s="52"/>
       <c r="Q187" s="52"/>
@@ -11154,13 +11262,13 @@
     </row>
     <row r="188" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D188" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="E188" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F188" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P188" s="78"/>
       <c r="Q188" s="78"/>
@@ -11174,13 +11282,13 @@
     </row>
     <row r="189" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D189" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E189" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="F189" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P189" s="52"/>
       <c r="Q189" s="52"/>
@@ -11194,13 +11302,13 @@
     </row>
     <row r="190" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D190" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="E190" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="F190" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P190" s="78"/>
       <c r="Q190" s="52"/>
@@ -11214,13 +11322,13 @@
     </row>
     <row r="191" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D191" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="E191" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="F191" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P191" s="78"/>
       <c r="Q191" s="52"/>
@@ -11234,13 +11342,13 @@
     </row>
     <row r="192" spans="4:27" x14ac:dyDescent="0.25">
       <c r="D192" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E192" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="F192" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P192" s="78"/>
       <c r="Q192" s="78"/>
@@ -11253,13 +11361,13 @@
     </row>
     <row r="193" spans="4:24" x14ac:dyDescent="0.25">
       <c r="D193" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="E193" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F193" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P193" s="78"/>
       <c r="Q193" s="78"/>
@@ -11272,13 +11380,13 @@
     </row>
     <row r="194" spans="4:24" x14ac:dyDescent="0.25">
       <c r="D194" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E194" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="F194" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P194" s="52"/>
       <c r="Q194" s="52"/>
@@ -11291,13 +11399,13 @@
     </row>
     <row r="195" spans="4:24" x14ac:dyDescent="0.25">
       <c r="D195" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="E195" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="F195" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P195" s="78"/>
       <c r="Q195" s="78"/>
@@ -11310,13 +11418,13 @@
     </row>
     <row r="196" spans="4:24" x14ac:dyDescent="0.25">
       <c r="D196" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E196" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="F196" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P196" s="78"/>
       <c r="Q196" s="78"/>
@@ -11329,13 +11437,13 @@
     </row>
     <row r="197" spans="4:24" x14ac:dyDescent="0.25">
       <c r="D197" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="E197" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="F197" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P197" s="78"/>
       <c r="Q197" s="78"/>
@@ -11348,13 +11456,13 @@
     </row>
     <row r="198" spans="4:24" x14ac:dyDescent="0.25">
       <c r="D198" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E198" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="F198" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P198" s="52"/>
       <c r="Q198" s="52"/>
@@ -11367,13 +11475,13 @@
     </row>
     <row r="199" spans="4:24" x14ac:dyDescent="0.25">
       <c r="D199" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="E199" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F199" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P199" s="52"/>
       <c r="Q199" s="52"/>
@@ -11386,13 +11494,13 @@
     </row>
     <row r="200" spans="4:24" x14ac:dyDescent="0.25">
       <c r="D200" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E200" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F200" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P200" s="78"/>
       <c r="Q200" s="78"/>
@@ -11405,13 +11513,13 @@
     </row>
     <row r="201" spans="4:24" x14ac:dyDescent="0.25">
       <c r="D201" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="E201" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="F201" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P201" s="78"/>
       <c r="R201" s="78"/>
@@ -11423,13 +11531,13 @@
     </row>
     <row r="202" spans="4:24" x14ac:dyDescent="0.25">
       <c r="D202" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="E202" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F202" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P202" s="78"/>
       <c r="Q202" s="78"/>
@@ -11442,13 +11550,13 @@
     </row>
     <row r="203" spans="4:24" x14ac:dyDescent="0.25">
       <c r="D203" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="E203" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="F203" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P203" s="78"/>
       <c r="Q203" s="78"/>
@@ -11461,13 +11569,13 @@
     </row>
     <row r="204" spans="4:24" x14ac:dyDescent="0.25">
       <c r="D204" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="E204" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="F204" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P204" s="52"/>
       <c r="Q204" s="52"/>
@@ -11480,13 +11588,13 @@
     </row>
     <row r="205" spans="4:24" x14ac:dyDescent="0.25">
       <c r="D205" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="E205" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="F205" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P205" s="52"/>
       <c r="Q205" s="52"/>
@@ -11498,13 +11606,13 @@
     </row>
     <row r="206" spans="4:24" x14ac:dyDescent="0.25">
       <c r="D206" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E206" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="F206" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P206" s="52"/>
       <c r="Q206" s="52"/>
@@ -11516,13 +11624,13 @@
     </row>
     <row r="207" spans="4:24" x14ac:dyDescent="0.25">
       <c r="D207" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="E207" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F207" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P207" s="52"/>
       <c r="Q207" s="52"/>
@@ -11534,13 +11642,13 @@
     </row>
     <row r="208" spans="4:24" x14ac:dyDescent="0.25">
       <c r="D208" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E208" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="F208" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P208" s="78"/>
       <c r="Q208" s="78"/>
@@ -11552,13 +11660,13 @@
     </row>
     <row r="209" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D209" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E209" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F209" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="P209" s="52"/>
       <c r="Q209" s="52"/>
@@ -11570,13 +11678,13 @@
     </row>
     <row r="210" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D210" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E210" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F210" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="P210" s="78"/>
       <c r="Q210" s="78"/>
@@ -11588,13 +11696,13 @@
     </row>
     <row r="211" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D211" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="E211" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F211" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="P211" s="78"/>
       <c r="Q211" s="52"/>
@@ -11606,13 +11714,13 @@
     </row>
     <row r="212" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D212" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="E212" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="F212" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P212" s="52"/>
       <c r="Q212" s="52"/>
@@ -11624,13 +11732,13 @@
     </row>
     <row r="213" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D213" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="E213" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="F213" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P213" s="52"/>
       <c r="Q213" s="52"/>
@@ -11642,13 +11750,13 @@
     </row>
     <row r="214" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D214" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="E214" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F214" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P214" s="52"/>
       <c r="Q214" s="52"/>
@@ -11660,13 +11768,13 @@
     </row>
     <row r="215" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D215" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="E215" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="F215" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P215" s="78"/>
       <c r="Q215" s="78"/>
@@ -11678,13 +11786,13 @@
     </row>
     <row r="216" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D216" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="E216" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="F216" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P216" s="78"/>
       <c r="Q216" s="78"/>
@@ -11696,13 +11804,13 @@
     </row>
     <row r="217" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D217" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E217" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="F217" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P217" s="78"/>
       <c r="Q217" s="78"/>
@@ -11714,13 +11822,13 @@
     </row>
     <row r="218" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D218" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E218" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F218" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P218" s="52"/>
       <c r="Q218" s="52"/>
@@ -11732,13 +11840,13 @@
     </row>
     <row r="219" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D219" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="E219" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="F219" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P219" s="78"/>
       <c r="Q219" s="78"/>
@@ -11750,13 +11858,13 @@
     </row>
     <row r="220" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D220" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E220" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="F220" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P220" s="78"/>
       <c r="Q220" s="78"/>
@@ -11768,13 +11876,13 @@
     </row>
     <row r="221" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D221" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="E221" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="F221" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P221" s="78"/>
       <c r="Q221" s="52"/>
@@ -11786,13 +11894,13 @@
     </row>
     <row r="222" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D222" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="E222" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="F222" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P222" s="52"/>
       <c r="Q222" s="52"/>
@@ -11804,13 +11912,13 @@
     </row>
     <row r="223" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D223" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="E223" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="F223" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P223" s="78"/>
       <c r="Q223" s="52"/>
@@ -11822,13 +11930,13 @@
     </row>
     <row r="224" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D224" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="E224" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F224" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P224" s="89"/>
       <c r="Q224" s="90"/>
@@ -11840,13 +11948,13 @@
     </row>
     <row r="225" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D225" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="E225" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F225" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P225" s="89"/>
       <c r="Q225" s="90"/>
@@ -11858,13 +11966,13 @@
     </row>
     <row r="226" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D226" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="E226" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="F226" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P226" s="89"/>
       <c r="Q226" s="90"/>
@@ -11876,13 +11984,13 @@
     </row>
     <row r="227" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D227" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="E227" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="F227" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P227" s="89"/>
       <c r="Q227" s="90"/>
@@ -11894,13 +12002,13 @@
     </row>
     <row r="228" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D228" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="E228" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="F228" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P228" s="89"/>
       <c r="Q228" s="90"/>
@@ -11912,13 +12020,13 @@
     </row>
     <row r="229" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D229" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="E229" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="F229" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P229" s="89"/>
       <c r="Q229" s="90"/>
@@ -11930,13 +12038,13 @@
     </row>
     <row r="230" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D230" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="E230" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="F230" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P230" s="89"/>
       <c r="Q230" s="90"/>
@@ -11948,13 +12056,13 @@
     </row>
     <row r="231" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D231" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E231" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="F231" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P231" s="89"/>
       <c r="Q231" s="90"/>
@@ -11966,13 +12074,13 @@
     </row>
     <row r="232" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D232" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="E232" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="F232" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P232" s="89"/>
       <c r="Q232" s="90"/>
@@ -11984,13 +12092,13 @@
     </row>
     <row r="233" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D233" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="E233" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F233" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P233" s="89"/>
       <c r="Q233" s="90"/>
@@ -12002,1378 +12110,1378 @@
     </row>
     <row r="234" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D234" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="E234" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="F234" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P234" s="92"/>
     </row>
     <row r="235" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D235" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E235" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="F235" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P235" s="92"/>
     </row>
     <row r="236" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D236" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="E236" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="F236" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="P236" s="92"/>
     </row>
     <row r="237" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D237" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E237" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F237" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P237" s="92"/>
     </row>
     <row r="238" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D238" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E238" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F238" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P238" s="92"/>
     </row>
     <row r="239" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D239" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E239" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="F239" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P239" s="92"/>
     </row>
     <row r="240" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D240" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="E240" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="F240" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P240" s="92"/>
     </row>
     <row r="241" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D241" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E241" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="F241" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P241" s="92"/>
     </row>
     <row r="242" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D242" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E242" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="F242" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P242" s="92"/>
     </row>
     <row r="243" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D243" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="E243" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="F243" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P243" s="92"/>
     </row>
     <row r="244" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D244" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E244" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="F244" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="P244" s="92"/>
     </row>
     <row r="245" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D245" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E245" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="F245" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="P245" s="92"/>
     </row>
     <row r="246" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D246" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="E246" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="F246" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P246" s="92"/>
     </row>
     <row r="247" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D247" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E247" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="F247" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P247" s="92"/>
     </row>
     <row r="248" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D248" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E248" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F248" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P248" s="92"/>
     </row>
     <row r="249" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D249" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E249" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F249" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="P249" s="92"/>
     </row>
     <row r="250" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D250" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E250" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="F250" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P250" s="92"/>
     </row>
     <row r="251" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D251" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="E251" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="F251" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P251" s="92"/>
     </row>
     <row r="252" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D252" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="E252" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="F252" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P252" s="92"/>
     </row>
     <row r="253" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D253" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="E253" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="F253" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P253" s="92"/>
     </row>
     <row r="254" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D254" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="E254" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="F254" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P254" s="92"/>
     </row>
     <row r="255" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D255" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E255" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="F255" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="P255" s="92"/>
     </row>
     <row r="256" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D256" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="E256" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F256" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P256" s="92"/>
     </row>
     <row r="257" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D257" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E257" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F257" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P257" s="92"/>
     </row>
     <row r="258" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D258" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E258" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="F258" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P258" s="92"/>
     </row>
     <row r="259" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D259" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E259" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F259" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P259" s="92"/>
     </row>
     <row r="260" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D260" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E260" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F260" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P260" s="92"/>
     </row>
     <row r="261" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D261" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E261" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F261" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P261" s="92"/>
     </row>
     <row r="262" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D262" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E262" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="F262" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P262" s="92"/>
     </row>
     <row r="263" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D263" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E263" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="F263" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P263" s="92"/>
     </row>
     <row r="264" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D264" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="E264" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="F264" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P264" s="92"/>
     </row>
     <row r="265" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D265" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="E265" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="F265" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P265" s="92"/>
     </row>
     <row r="266" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D266" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="E266" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="F266" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P266" s="92"/>
     </row>
     <row r="267" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D267" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="E267" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="F267" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P267" s="92"/>
     </row>
     <row r="268" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D268" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="E268" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="F268" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P268" s="92"/>
     </row>
     <row r="269" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D269" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E269" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="F269" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P269" s="92"/>
     </row>
     <row r="270" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D270" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="E270" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="F270" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P270" s="92"/>
     </row>
     <row r="271" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D271" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="E271" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="F271" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P271" s="92"/>
     </row>
     <row r="272" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D272" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="E272" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="F272" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P272" s="92"/>
     </row>
     <row r="273" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D273" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E273" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="F273" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P273" s="92"/>
     </row>
     <row r="274" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D274" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E274" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F274" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P274" s="92"/>
     </row>
     <row r="275" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D275" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E275" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F275" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P275" s="92"/>
     </row>
     <row r="276" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D276" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E276" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F276" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P276" s="92"/>
     </row>
     <row r="277" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D277" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="E277" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="F277" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P277" s="92"/>
     </row>
     <row r="278" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D278" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="E278" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="F278" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P278" s="92"/>
     </row>
     <row r="279" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D279" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="E279" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="F279" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P279" s="92"/>
     </row>
     <row r="280" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D280" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="E280" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="F280" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P280" s="92"/>
     </row>
     <row r="281" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D281" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="E281" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="F281" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P281" s="92"/>
     </row>
     <row r="282" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D282" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="E282" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="F282" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P282" s="92"/>
     </row>
     <row r="283" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D283" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E283" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="F283" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P283" s="92"/>
     </row>
     <row r="284" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D284" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E284" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F284" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P284" s="92"/>
     </row>
     <row r="285" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D285" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="E285" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="F285" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P285" s="92"/>
     </row>
     <row r="286" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D286" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="E286" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="F286" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P286" s="92"/>
     </row>
     <row r="287" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D287" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E287" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="F287" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P287" s="92"/>
     </row>
     <row r="288" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D288" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="E288" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="F288" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P288" s="92"/>
     </row>
     <row r="289" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D289" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="E289" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="F289" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P289" s="92"/>
     </row>
     <row r="290" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D290" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="E290" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="F290" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P290" s="92"/>
     </row>
     <row r="291" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D291" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="E291" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="F291" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P291" s="92"/>
     </row>
     <row r="292" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D292" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="E292" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="F292" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P292" s="92"/>
     </row>
     <row r="293" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D293" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="E293" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="F293" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P293" s="92"/>
     </row>
     <row r="294" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D294" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="E294" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="F294" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P294" s="92"/>
     </row>
     <row r="295" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D295" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="E295" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="F295" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P295" s="92"/>
     </row>
     <row r="296" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D296" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E296" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="F296" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P296" s="92"/>
     </row>
     <row r="297" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D297" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E297" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F297" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="P297" s="92"/>
     </row>
     <row r="298" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D298" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="E298" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="F298" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P298" s="92"/>
     </row>
     <row r="299" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D299" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="E299" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="F299" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P299" s="92"/>
     </row>
     <row r="300" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D300" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E300" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="F300" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P300" s="92"/>
     </row>
     <row r="301" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D301" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="E301" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="F301" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P301" s="92"/>
     </row>
     <row r="302" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D302" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="E302" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="F302" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P302" s="92"/>
     </row>
     <row r="303" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D303" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="E303" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="F303" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P303" s="92"/>
     </row>
     <row r="304" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D304" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="E304" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="F304" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P304" s="92"/>
     </row>
     <row r="305" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D305" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="E305" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="F305" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P305" s="92"/>
     </row>
     <row r="306" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D306" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="E306" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="F306" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P306" s="92"/>
     </row>
     <row r="307" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D307" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="E307" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="F307" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P307" s="92"/>
     </row>
     <row r="308" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D308" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="E308" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="F308" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P308" s="92"/>
     </row>
     <row r="309" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D309" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="E309" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="F309" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P309" s="92"/>
     </row>
     <row r="310" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D310" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="E310" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="F310" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P310" s="92"/>
     </row>
     <row r="311" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D311" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="E311" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="F311" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P311" s="92"/>
     </row>
     <row r="312" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D312" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="E312" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="F312" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P312" s="92"/>
     </row>
     <row r="313" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D313" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="E313" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="F313" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P313" s="92"/>
     </row>
     <row r="314" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D314" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E314" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="F314" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P314" s="92"/>
     </row>
     <row r="315" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D315" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="E315" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="F315" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P315" s="92"/>
     </row>
     <row r="316" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D316" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E316" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="F316" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P316" s="92"/>
     </row>
     <row r="317" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D317" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="E317" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="F317" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P317" s="92"/>
     </row>
     <row r="318" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D318" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="E318" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="F318" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P318" s="92"/>
     </row>
     <row r="319" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D319" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="E319" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F319" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P319" s="92"/>
     </row>
     <row r="320" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D320" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="E320" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="F320" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P320" s="92"/>
     </row>
     <row r="321" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D321" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="E321" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="F321" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P321" s="92"/>
     </row>
     <row r="322" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D322" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="E322" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="F322" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P322" s="92"/>
     </row>
     <row r="323" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D323" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="E323" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="F323" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P323" s="92"/>
     </row>
     <row r="324" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D324" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="E324" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="F324" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P324" s="92"/>
     </row>
     <row r="325" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D325" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="E325" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F325" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P325" s="92"/>
     </row>
     <row r="326" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D326" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="E326" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="F326" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P326" s="92"/>
     </row>
     <row r="327" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D327" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="E327" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="F327" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P327" s="92"/>
     </row>
     <row r="328" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D328" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E328" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="F328" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P328" s="92"/>
     </row>
     <row r="329" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D329" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="E329" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F329" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P329" s="92"/>
     </row>
     <row r="330" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D330" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="E330" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F330" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P330" s="92"/>
     </row>
     <row r="331" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D331" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="E331" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F331" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P331" s="92"/>
     </row>
     <row r="332" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D332" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E332" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F332" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="P332" s="92"/>
     </row>
     <row r="333" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D333" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="E333" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="F333" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P333" s="92"/>
     </row>
     <row r="334" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D334" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="E334" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="F334" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P334" s="92"/>
     </row>
     <row r="335" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D335" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E335" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="F335" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P335" s="92"/>
     </row>
     <row r="336" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D336" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E336" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F336" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P336" s="92"/>
     </row>
     <row r="337" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D337" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="E337" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="F337" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P337" s="92"/>
     </row>
     <row r="338" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D338" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="E338" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="F338" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P338" s="92"/>
     </row>
     <row r="339" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D339" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="E339" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F339" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P339" s="92"/>
     </row>
     <row r="340" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D340" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="E340" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="F340" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P340" s="92"/>
     </row>
     <row r="341" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D341" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="E341" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F341" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P341" s="92"/>
     </row>
     <row r="342" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D342" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="E342" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="F342" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P342" s="92"/>
     </row>
     <row r="343" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D343" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="E343" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="F343" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P343" s="92"/>
     </row>
     <row r="344" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D344" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="E344" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="F344" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P344" s="92"/>
     </row>
     <row r="345" spans="4:16" x14ac:dyDescent="0.25">
       <c r="E345" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="F345" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="P345" s="92"/>
     </row>
     <row r="346" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D346" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="E346" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="F346" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="P346" s="92"/>
     </row>
     <row r="347" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D347" s="86" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="E347" s="86" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="F347" s="86" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="P347" s="92"/>
     </row>
     <row r="348" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D348" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="E348" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F348" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P348" s="92"/>
     </row>
@@ -13382,130 +13490,130 @@
         <v>0</v>
       </c>
       <c r="E349" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="F349" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="P349" s="92"/>
     </row>
     <row r="350" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D350" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="E350" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="F350" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="P350" s="92"/>
     </row>
     <row r="351" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D351" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="E351" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F351" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P351" s="92"/>
     </row>
     <row r="352" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D352" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="E352" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="F352" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P352" s="92"/>
     </row>
     <row r="353" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D353" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E353" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="F353" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="P353" s="92"/>
     </row>
     <row r="354" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D354" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E354" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F354" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P354" s="92"/>
     </row>
     <row r="355" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D355" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="E355" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="F355" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P355" s="92"/>
     </row>
     <row r="356" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D356" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="E356" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="F356" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P356" s="92"/>
     </row>
     <row r="357" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D357" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="E357" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="F357" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="P357" s="92"/>
     </row>
     <row r="358" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D358" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="E358" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="F358" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="P358" s="92"/>
     </row>
     <row r="359" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D359" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="E359" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="F359" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="P359" s="92"/>
     </row>
@@ -14858,7 +14966,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451DC71D-A65B-4AC5-B117-130613ABA0E8}">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="71.42578125" style="25" bestFit="1" customWidth="1"/>
@@ -15142,11 +15250,11 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B11" s="7" t="str">
         <f>VLOOKUP(A11,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SALUD</v>
+        <v>TR DIGI</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>9</v>
@@ -15158,22 +15266,22 @@
         <v>11</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B12" s="7" t="str">
         <f>VLOOKUP(A12,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>TR DIGI</v>
+        <v>OPER</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>9</v>
@@ -15185,22 +15293,22 @@
         <v>11</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="B13" s="7" t="str">
         <f>VLOOKUP(A13,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>OPER</v>
+        <v>BI</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>9</v>
@@ -15212,22 +15320,22 @@
         <v>11</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>58</v>
+      <c r="A14" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="B14" s="7" t="str">
         <f>VLOOKUP(A14,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>BRAND</v>
+        <v>BI</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>9</v>
@@ -15235,26 +15343,26 @@
       <c r="D14" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="13" t="s">
-        <v>59</v>
+      <c r="E14" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="B15" s="7" t="str">
         <f>VLOOKUP(A15,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>COACH</v>
+        <v>PROD</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>9</v>
@@ -15262,26 +15370,26 @@
       <c r="D15" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>59</v>
+      <c r="E15" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B16" s="7" t="str">
         <f>VLOOKUP(A16,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>CX</v>
+        <v>BRAND</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>9</v>
@@ -15293,22 +15401,22 @@
         <v>59</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B17" s="7" t="str">
         <f>VLOOKUP(A17,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>DERECHO</v>
+        <v>COACH</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>9</v>
@@ -15320,22 +15428,22 @@
         <v>59</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B18" s="7" t="str">
         <f>VLOOKUP(A18,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>MKT GC</v>
+        <v>CX</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>9</v>
@@ -15347,22 +15455,22 @@
         <v>59</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="97" t="s">
-        <v>558</v>
+      <c r="A19" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="B19" s="7" t="str">
         <f>VLOOKUP(A19,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>MKT EC</v>
+        <v>MKT GC</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>9</v>
@@ -15374,18 +15482,18 @@
         <v>59</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>78</v>
+      <c r="A20" s="93" t="s">
+        <v>554</v>
       </c>
       <c r="B20" s="7" t="str">
         <f>VLOOKUP(A20,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
@@ -15412,11 +15520,11 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B21" s="7" t="str">
         <f>VLOOKUP(A21,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>NEURO MKT</v>
+        <v>MKT EC</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>9</v>
@@ -15428,22 +15536,22 @@
         <v>59</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B22" s="7" t="str">
         <f>VLOOKUP(A22,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>VENTAS</v>
+        <v>NEURO MKT</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>9</v>
@@ -15455,22 +15563,22 @@
         <v>59</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B23" s="7" t="str">
         <f>VLOOKUP(A23,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>DERECHO DIG.</v>
+        <v>VENTAS</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>9</v>
@@ -15482,22 +15590,22 @@
         <v>59</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="B24" s="7" t="str">
         <f>VLOOKUP(A24,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>PROD</v>
+        <v>DERECHO</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>9</v>
@@ -15506,25 +15614,25 @@
         <v>10</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="B25" s="7" t="str">
         <f>VLOOKUP(A25,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>RSC</v>
+        <v>SALUD</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>9</v>
@@ -15533,25 +15641,25 @@
         <v>10</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>101</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B26" s="7" t="str">
         <f>VLOOKUP(A26,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SOSTEN</v>
+        <v>RSC</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>9</v>
@@ -15560,25 +15668,25 @@
         <v>10</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B27" s="7" t="str">
         <f>VLOOKUP(A27,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>BI</v>
+        <v>SOSTEN</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>9</v>
@@ -15587,25 +15695,25 @@
         <v>10</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>109</v>
+      <c r="A28" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="B28" s="7" t="str">
         <f>VLOOKUP(A28,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>BI</v>
+        <v>CIBER</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>9</v>
@@ -15614,13 +15722,13 @@
         <v>10</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F28" s="10" t="s">
         <v>107</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H28" s="10" t="s">
         <v>108</v>
@@ -15628,11 +15736,11 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B29" s="7" t="str">
         <f>VLOOKUP(A29,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>CIBER</v>
+        <v>GDATA</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>9</v>
@@ -15641,10 +15749,10 @@
         <v>10</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G29" s="11" t="s">
         <v>111</v>
@@ -15659,7 +15767,7 @@
       </c>
       <c r="B30" s="7" t="str">
         <f>VLOOKUP(A30,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>GDATA</v>
+        <v>IA</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>9</v>
@@ -15668,7 +15776,7 @@
         <v>10</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F30" s="10" t="s">
         <v>114</v>
@@ -15677,16 +15785,16 @@
         <v>115</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B31" s="7" t="str">
         <f>VLOOKUP(A31,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>IA</v>
+        <v>PM ESP</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>9</v>
@@ -15695,13 +15803,13 @@
         <v>10</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F31" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="G31" s="11" t="s">
         <v>118</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>119</v>
       </c>
       <c r="H31" s="10" t="s">
         <v>119</v>
@@ -15713,7 +15821,7 @@
       </c>
       <c r="B32" s="7" t="str">
         <f>VLOOKUP(A32,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>PM ESP</v>
+        <v>SISTEM</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>9</v>
@@ -15722,7 +15830,7 @@
         <v>10</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>121</v>
@@ -15735,12 +15843,12 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="15" t="s">
         <v>124</v>
       </c>
       <c r="B33" s="7" t="str">
         <f>VLOOKUP(A33,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SISTEM</v>
+        <v>FULL</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>9</v>
@@ -15749,7 +15857,7 @@
         <v>10</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>125</v>
@@ -15762,7 +15870,7 @@
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="12" t="s">
         <v>128</v>
       </c>
       <c r="B34" s="7" t="str">
@@ -15776,25 +15884,25 @@
         <v>10</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F34" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="15" t="s">
         <v>129</v>
-      </c>
-      <c r="G34" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
-        <v>132</v>
       </c>
       <c r="B35" s="7" t="str">
         <f>VLOOKUP(A35,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>FULL</v>
+        <v>DEVOPS</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>9</v>
@@ -15803,16 +15911,16 @@
         <v>10</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -15821,7 +15929,7 @@
       </c>
       <c r="B36" s="7" t="str">
         <f>VLOOKUP(A36,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>DEVOPS</v>
+        <v>BIG DATA</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>9</v>
@@ -15830,7 +15938,7 @@
         <v>10</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F36" s="10" t="s">
         <v>134</v>
@@ -15843,129 +15951,129 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="12" t="s">
         <v>137</v>
       </c>
       <c r="B37" s="7" t="str">
         <f>VLOOKUP(A37,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>BIG DATA</v>
+        <v>IBM ENG</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>95</v>
+        <v>138</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>139</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B38" s="7" t="str">
         <f>VLOOKUP(A38,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>IBM ENG</v>
+        <v>EMBA ENG</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>9</v>
+        <v>143</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F38" s="10" t="s">
         <v>144</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H38" s="10" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="17" t="s">
         <v>146</v>
       </c>
       <c r="B39" s="7" t="str">
         <f>VLOOKUP(A39,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>EMBA ENG</v>
+        <v>RSC ENG</v>
       </c>
       <c r="C39" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="F39" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="E39" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="F39" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="G39" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="H39" s="10" t="s">
+      <c r="H39" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="12" t="s">
         <v>149</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="17" t="s">
-        <v>150</v>
       </c>
       <c r="B40" s="7" t="str">
         <f>VLOOKUP(A40,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>RSC ENG</v>
+        <v>PM ENG</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>147</v>
+        <v>9</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F40" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="G40" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="G40" s="11" t="s">
+      <c r="H40" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="H40" s="11" t="s">
-        <v>152</v>
-      </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="18" t="s">
         <v>153</v>
       </c>
       <c r="B41" s="7" t="str">
         <f>VLOOKUP(A41,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>PM ENG</v>
+        <v>MKT EC ENG</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>154</v>
@@ -15973,56 +16081,56 @@
       <c r="G41" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="H41" s="10" t="s">
+      <c r="H41" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="15" t="s">
         <v>156</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="18" t="s">
-        <v>157</v>
       </c>
       <c r="B42" s="7" t="str">
         <f>VLOOKUP(A42,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>MKT EC ENG</v>
+        <v>SUPPLY ENG</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F42" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="G42" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="G42" s="11" t="s">
+      <c r="H42" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="H42" s="11" t="s">
-        <v>159</v>
-      </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="12" t="s">
         <v>160</v>
       </c>
       <c r="B43" s="7" t="str">
         <f>VLOOKUP(A43,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SUPPLY ENG</v>
+        <v>EMBA ESP</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>9</v>
+        <v>143</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="E43" s="16" t="s">
-        <v>143</v>
+        <v>10</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>161</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G43" s="11" t="s">
         <v>162</v>
@@ -16037,111 +16145,96 @@
       </c>
       <c r="B44" s="7" t="str">
         <f>VLOOKUP(A44,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>EMBA ESP</v>
+        <v>GMBA</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>10</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F44" s="10" t="s">
         <v>164</v>
       </c>
       <c r="G44" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="20" t="s">
         <v>166</v>
-      </c>
-      <c r="H44" s="10" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="12" t="s">
-        <v>168</v>
       </c>
       <c r="B45" s="7" t="str">
         <f>VLOOKUP(A45,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>GMBA</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="D45" s="8" t="s">
+        <v>TMBA</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D45" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="E45" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="G45" s="11" t="s">
-        <v>168</v>
+      <c r="E45" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="F45" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="G45" s="24" t="s">
+        <v>166</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="B46" s="7" t="str">
-        <f>VLOOKUP(A46,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>TMBA</v>
-      </c>
-      <c r="C46" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="D46" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="E46" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="F46" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="G46" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E48"/>
-      <c r="F48"/>
-      <c r="G48"/>
-      <c r="H48"/>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E47"/>
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="H47"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A41:A46 A2:B2 A11:A18 A3:A9 A20:A39 B3:B46">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  <conditionalFormatting sqref="A20">
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A19">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="A40:A45 A2:B2 A3:A9 A21:A38 A11:A19 B3:B45">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d5406e40fd28c5e817779a822da0a175">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6b7e0cdc028a074783d87c1f5297bb23" ns2:_="" ns3:_="">
     <xsd:import namespace="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
@@ -16370,28 +16463,12 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FF30BE2-8C49-4FF9-8831-BD9CB6638F8C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42E1AB7D-C01B-4FFE-9B42-D6ED241A40A7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16406,9 +16483,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42E1AB7D-C01B-4FFE-9B42-D6ED241A40A7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FF30BE2-8C49-4FF9-8831-BD9CB6638F8C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
+    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Areas_Paises.xlsx
+++ b/Areas_Paises.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{A8E03CFD-D3C2-4BD9-85BF-A581898274A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A734805F-411F-45BD-8C1A-006D80213915}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{A8E03CFD-D3C2-4BD9-85BF-A581898274A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{303007D5-4197-4F40-AB0E-69720AB92626}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{996CFF7E-4120-45EC-B5A3-4D8213062A4C}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Paises!$P$1:$V$225</definedName>
     <definedName name="PAISES">Paises!$A$1:$B$17</definedName>
     <definedName name="PILAR">Paises!$AF$1:$AG$18</definedName>
-    <definedName name="PROGRAMAS">Areas!$A$1:$G$46</definedName>
+    <definedName name="PROGRAMAS">Areas!$A$1:$G$47</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="560">
   <si>
     <t>PROGRAMA</t>
   </si>
@@ -1723,6 +1723,9 @@
   </si>
   <si>
     <t>COMERCIO</t>
+  </si>
+  <si>
+    <t>Máster de Formación Permanente en Marketing Digital, E-commerce e Inteligencia Artificial</t>
   </si>
 </sst>
 </file>
@@ -2346,29 +2349,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 4" xfId="2" xr:uid="{625F2583-C0A4-468A-84E4-A45687601707}"/>
   </cellStyles>
-  <dxfs count="47">
-    <dxf>
-      <border>
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="45">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3724,6 +3705,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="PROGRAMAS"/>
@@ -6597,6 +6579,247 @@
           </cell>
           <cell r="C358" t="str">
             <v>IA</v>
+          </cell>
+        </row>
+        <row r="359">
+          <cell r="B359" t="str">
+            <v>Máster de Dirección Permanente en Dirección y Automatización Industrial</v>
+          </cell>
+          <cell r="C359" t="str">
+            <v>PROD</v>
+          </cell>
+        </row>
+        <row r="360">
+          <cell r="B360" t="str">
+            <v>Máster de formación Permanente en Coaching directivo y liderazgo</v>
+          </cell>
+          <cell r="C360" t="str">
+            <v>COACH</v>
+          </cell>
+        </row>
+        <row r="361">
+          <cell r="B361" t="str">
+            <v>Máster de Formación permanente en Coaching diretivo y liderazgo</v>
+          </cell>
+          <cell r="C361" t="str">
+            <v>COACH</v>
+          </cell>
+        </row>
+        <row r="362">
+          <cell r="B362" t="str">
+            <v>Máster de Formación Permanente en Direcció de Marketing y Gestión Comercial</v>
+          </cell>
+          <cell r="C362" t="str">
+            <v>MKT GC</v>
+          </cell>
+        </row>
+        <row r="363">
+          <cell r="B363" t="str">
+            <v xml:space="preserve">Máster de Formación permanente en Marketing Digital, eCommerce e Inteligencia Artificial </v>
+          </cell>
+          <cell r="C363" t="str">
+            <v>MKT EC</v>
+          </cell>
+        </row>
+        <row r="364">
+          <cell r="B364" t="str">
+            <v>Máster de formación permanente en Project Management</v>
+          </cell>
+          <cell r="C364" t="str">
+            <v>PM ESP</v>
+          </cell>
+        </row>
+        <row r="365">
+          <cell r="B365" t="str">
+            <v>Máster de Formación Permanente en Supply Chain Management</v>
+          </cell>
+          <cell r="C365" t="str">
+            <v>SUPPLY</v>
+          </cell>
+        </row>
+        <row r="366">
+          <cell r="B366" t="str">
+            <v>Máster en  Ciberseguridad</v>
+          </cell>
+          <cell r="C366" t="str">
+            <v>CIBER</v>
+          </cell>
+        </row>
+        <row r="367">
+          <cell r="B367" t="str">
+            <v>Máster en Direccción de sistemas de la información</v>
+          </cell>
+          <cell r="C367" t="str">
+            <v>SISTEM</v>
+          </cell>
+        </row>
+        <row r="368">
+          <cell r="B368" t="str">
+            <v xml:space="preserve">Máster en Dirección de Comunicación </v>
+          </cell>
+          <cell r="C368" t="str">
+            <v>COMUNIC</v>
+          </cell>
+        </row>
+        <row r="369">
+          <cell r="B369" t="str">
+            <v>Máster en n Transformación Digital</v>
+          </cell>
+          <cell r="C369" t="str">
+            <v>TR DIGI</v>
+          </cell>
+        </row>
+        <row r="370">
+          <cell r="B370" t="str">
+            <v>Máster de Formación Permanente en Dirección de la Producción y Automatización Industrial -</v>
+          </cell>
+          <cell r="C370" t="str">
+            <v>PROD</v>
+          </cell>
+        </row>
+        <row r="371">
+          <cell r="B371" t="str">
+            <v xml:space="preserve">Máster en derecho internacional de la empresa </v>
+          </cell>
+          <cell r="C371" t="str">
+            <v>DERECHO</v>
+          </cell>
+        </row>
+        <row r="372">
+          <cell r="B372" t="str">
+            <v>Máster de Formación Permanente en Neuromarketing y comportamiento del consumidor</v>
+          </cell>
+          <cell r="C372" t="str">
+            <v>NEURO MKT</v>
+          </cell>
+        </row>
+        <row r="373">
+          <cell r="B373" t="str">
+            <v>Máster de Formación Permanente en Neuromarketing y Comportamiento del Consumidor</v>
+          </cell>
+          <cell r="C373" t="str">
+            <v>NEURO MKT</v>
+          </cell>
+        </row>
+        <row r="374">
+          <cell r="B374" t="str">
+            <v xml:space="preserve"> Máster de Formación Permanente en Neuromarketing y comportamiento del consumidor</v>
+          </cell>
+          <cell r="C374" t="str">
+            <v>NEURO MKT</v>
+          </cell>
+        </row>
+        <row r="375">
+          <cell r="B375" t="str">
+            <v xml:space="preserve">Máster de Formación Permanente en Neuromarketing y comportamiento del consumidor </v>
+          </cell>
+          <cell r="C375" t="str">
+            <v>NEURO MKT</v>
+          </cell>
+        </row>
+        <row r="376">
+          <cell r="B376" t="str">
+            <v>Lifelong Digital Marketing, E-Commerce and Artificial Intelligence</v>
+          </cell>
+          <cell r="C376" t="str">
+            <v>MKT EC</v>
+          </cell>
+        </row>
+        <row r="377">
+          <cell r="B377" t="str">
+            <v>Máster de Dirección Financiera</v>
+          </cell>
+          <cell r="C377" t="str">
+            <v>FINANC</v>
+          </cell>
+        </row>
+        <row r="378">
+          <cell r="B378" t="str">
+            <v>Máster de Formación Permanente en Branding y Estrategia de Marca -</v>
+          </cell>
+          <cell r="C378" t="str">
+            <v>BRAND</v>
+          </cell>
+        </row>
+        <row r="379">
+          <cell r="B379" t="str">
+            <v>Máster en Diección Estratégica de Operaciones e Innovación</v>
+          </cell>
+          <cell r="C379" t="str">
+            <v>OPER</v>
+          </cell>
+        </row>
+        <row r="380">
+          <cell r="B380" t="str">
+            <v>Máster en Fintech e innovación financiera</v>
+          </cell>
+          <cell r="C380" t="str">
+            <v>FINTECH</v>
+          </cell>
+        </row>
+        <row r="381">
+          <cell r="B381" t="str">
+            <v>Máster de Formación Permanente en Marketing Digital, E-commerce e Inteligencia Artificial</v>
+          </cell>
+          <cell r="C381" t="str">
+            <v>MKT EC</v>
+          </cell>
+        </row>
+        <row r="382">
+          <cell r="B382" t="str">
+            <v>Máster de Formación Permanente en  Customer Experience Management</v>
+          </cell>
+          <cell r="C382" t="str">
+            <v>CX</v>
+          </cell>
+        </row>
+        <row r="383">
+          <cell r="B383" t="str">
+            <v>Máster de Formación Permanente en Business Intelligence &amp; Data Analytics</v>
+          </cell>
+          <cell r="C383" t="str">
+            <v>BI</v>
+          </cell>
+        </row>
+        <row r="384">
+          <cell r="B384" t="str">
+            <v>Máster de Formación Permanente en Coaching, Liderazgo Directivo e Inteligencia Emocional</v>
+          </cell>
+          <cell r="C384" t="str">
+            <v>COACH</v>
+          </cell>
+        </row>
+        <row r="385">
+          <cell r="B385" t="str">
+            <v>Marketing Digital, eCommerce e
+Inteligencia Artificial</v>
+          </cell>
+          <cell r="C385" t="str">
+            <v>MKT EC</v>
+          </cell>
+        </row>
+        <row r="386">
+          <cell r="B386" t="str">
+            <v>Máster de Formación Permanente en Responsabilidad Social Corporativa y Liderazgo Sostenibl</v>
+          </cell>
+          <cell r="C386" t="str">
+            <v>RSC</v>
+          </cell>
+        </row>
+        <row r="387">
+          <cell r="B387" t="str">
+            <v>Máster de Formación Permanente en Supply Chain Management y Logística -</v>
+          </cell>
+          <cell r="C387" t="str">
+            <v>SUPPLY</v>
+          </cell>
+        </row>
+        <row r="388">
+          <cell r="B388" t="str">
+            <v>Máster en Business Intelligence &amp; Data Analytics</v>
+          </cell>
+          <cell r="C388" t="str">
+            <v>BI</v>
           </cell>
         </row>
       </sheetData>
@@ -14907,128 +15130,128 @@
     <mergeCell ref="BH32:BH41"/>
   </mergeCells>
   <conditionalFormatting sqref="A28:A30 A43:A1048576 A1:A26">
-    <cfRule type="duplicateValues" dxfId="46" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D357:D1048576 D1:D351">
-    <cfRule type="duplicateValues" dxfId="45" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P42">
-    <cfRule type="duplicateValues" dxfId="44" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P180">
-    <cfRule type="duplicateValues" dxfId="43" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P193:P194">
-    <cfRule type="duplicateValues" dxfId="42" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P196:P198">
-    <cfRule type="duplicateValues" dxfId="41" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P199">
-    <cfRule type="duplicateValues" dxfId="40" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P204">
-    <cfRule type="duplicateValues" dxfId="39" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P208">
-    <cfRule type="duplicateValues" dxfId="38" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P209">
-    <cfRule type="duplicateValues" dxfId="37" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P216 P195 P181:P184 P191:P192 P200:P203 P205:P207 P211:P212 P218:P1048576 P43:P68 P1:P11 P40 P73:P146 P13:P38 P70:P71 P148:P179">
-    <cfRule type="duplicateValues" dxfId="36" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P217">
-    <cfRule type="duplicateValues" dxfId="35" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P210:Q210">
-    <cfRule type="duplicateValues" dxfId="34" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q46">
-    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q47">
-    <cfRule type="duplicateValues" dxfId="32" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q117">
-    <cfRule type="duplicateValues" dxfId="31" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q139">
-    <cfRule type="duplicateValues" dxfId="30" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q176">
-    <cfRule type="duplicateValues" dxfId="29" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q216:Q1048576 Q140:Q146 Q177:Q209 Q211:Q212 Q48:Q71 Q1:Q27 Q118:Q138 Q40 Q74:Q116 Q42:Q45 Q29:Q38 Q148:Q175">
-    <cfRule type="duplicateValues" dxfId="28" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R117">
-    <cfRule type="duplicateValues" dxfId="27" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R173">
-    <cfRule type="duplicateValues" dxfId="26" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R216:R1048576 R174:R212 R1:R38 R118:R146 R40 R73:R116 R42:R71 R148:R172">
-    <cfRule type="duplicateValues" dxfId="25" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="S88:T88 S97:T97 S102:T102 S104:T104 S111:T111 S115:T115 S120:T120 S127:T127 S130:T130 S133:T133 S145:T145 S156:T157 S165:T165 S174:T174">
-    <cfRule type="expression" dxfId="24" priority="29">
+    <cfRule type="expression" dxfId="22" priority="29">
       <formula>$S88=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X110">
-    <cfRule type="duplicateValues" dxfId="23" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC1:AC1048576 AI19:AI1048576">
-    <cfRule type="expression" dxfId="22" priority="34">
+    <cfRule type="expression" dxfId="20" priority="34">
       <formula>$AD1="ko"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD76 AA2:AA191">
-    <cfRule type="cellIs" dxfId="21" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="35" operator="equal">
       <formula>"ko"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="36" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI1">
-    <cfRule type="expression" dxfId="19" priority="33">
+    <cfRule type="expression" dxfId="17" priority="33">
       <formula>$AD1="ko"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ13">
-    <cfRule type="cellIs" dxfId="18" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="31" operator="equal">
       <formula>"ko"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="32" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ11:AQ21">
-    <cfRule type="duplicateValues" dxfId="16" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV21 AV25:AV29">
-    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
       <formula>"Estudios primarios"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="7" operator="equal">
       <formula>"Estudios secundarios"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW2:AW21 AW25:AW29">
-    <cfRule type="cellIs" dxfId="13" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="lessThan">
       <formula>21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AY2:AY21">
-    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
       <formula>"NOT VALID"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AY25:AY29">
-    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>"NOT VALID"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15053,7 +15276,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR51">
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15090,7 +15313,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451DC71D-A65B-4AC5-B117-130613ABA0E8}">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="71.42578125" style="25" bestFit="1" customWidth="1"/>
@@ -15643,8 +15866,8 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>74</v>
+      <c r="A21" t="s">
+        <v>559</v>
       </c>
       <c r="B21" s="7" t="str">
         <f>VLOOKUP(A21,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
@@ -15671,11 +15894,11 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B22" s="7" t="str">
         <f>VLOOKUP(A22,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>NEURO MKT</v>
+        <v>MKT EC</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>8</v>
@@ -15687,22 +15910,22 @@
         <v>55</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>551</v>
+        <v>78</v>
       </c>
       <c r="B23" s="7" t="str">
         <f>VLOOKUP(A23,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>DERECHO DIG.</v>
+        <v>NEURO MKT</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>8</v>
@@ -15714,22 +15937,22 @@
         <v>55</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>552</v>
+        <v>79</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>553</v>
+        <v>80</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>554</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>82</v>
+        <v>551</v>
       </c>
       <c r="B24" s="7" t="str">
         <f>VLOOKUP(A24,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>VENTAS</v>
+        <v>DERECHO DIG.</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>8</v>
@@ -15741,22 +15964,22 @@
         <v>55</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>83</v>
+        <v>552</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>84</v>
+        <v>553</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>85</v>
+        <v>554</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="B25" s="7" t="str">
         <f>VLOOKUP(A25,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>DERECHO</v>
+        <v>VENTAS</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>8</v>
@@ -15764,26 +15987,26 @@
       <c r="D25" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E25" s="14" t="s">
-        <v>87</v>
+      <c r="E25" s="13" t="s">
+        <v>55</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="B26" s="7" t="str">
         <f>VLOOKUP(A26,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SALUD</v>
+        <v>DERECHO</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>8</v>
@@ -15795,22 +16018,22 @@
         <v>87</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="B27" s="7" t="str">
         <f>VLOOKUP(A27,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>RSC</v>
+        <v>SALUD</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>8</v>
@@ -15822,22 +16045,22 @@
         <v>87</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B28" s="7" t="str">
         <f>VLOOKUP(A28,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SOSTEN</v>
+        <v>RSC</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>8</v>
@@ -15849,22 +16072,22 @@
         <v>87</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B29" s="7" t="str">
         <f>VLOOKUP(A29,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>CIBER</v>
+        <v>SOSTEN</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>8</v>
@@ -15876,22 +16099,22 @@
         <v>87</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B30" s="7" t="str">
         <f>VLOOKUP(A30,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>GDATA</v>
+        <v>CIBER</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>8</v>
@@ -15903,22 +16126,22 @@
         <v>87</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B31" s="7" t="str">
         <f>VLOOKUP(A31,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>IA</v>
+        <v>GDATA</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>8</v>
@@ -15930,22 +16153,22 @@
         <v>87</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B32" s="7" t="str">
         <f>VLOOKUP(A32,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>PM ESP</v>
+        <v>IA</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>8</v>
@@ -15957,22 +16180,22 @@
         <v>87</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B33" s="7" t="str">
         <f>VLOOKUP(A33,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SISTEM</v>
+        <v>PM ESP</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>8</v>
@@ -15984,22 +16207,22 @@
         <v>87</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
-        <v>120</v>
+      <c r="A34" s="12" t="s">
+        <v>116</v>
       </c>
       <c r="B34" s="7" t="str">
         <f>VLOOKUP(A34,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>FULL</v>
+        <v>SISTEM</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>8</v>
@@ -16011,18 +16234,18 @@
         <v>87</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="s">
-        <v>124</v>
+      <c r="A35" s="15" t="s">
+        <v>120</v>
       </c>
       <c r="B35" s="7" t="str">
         <f>VLOOKUP(A35,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
@@ -16048,12 +16271,12 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
-        <v>125</v>
+      <c r="A36" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="B36" s="7" t="str">
         <f>VLOOKUP(A36,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>DEVOPS</v>
+        <v>FULL</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>8</v>
@@ -16065,22 +16288,22 @@
         <v>87</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B37" s="7" t="str">
         <f>VLOOKUP(A37,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>BIG DATA</v>
+        <v>DEVOPS</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>8</v>
@@ -16092,52 +16315,52 @@
         <v>87</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="12" t="s">
-        <v>133</v>
+      <c r="A38" s="15" t="s">
+        <v>129</v>
       </c>
       <c r="B38" s="7" t="str">
         <f>VLOOKUP(A38,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>IBM ENG</v>
+        <v>BIG DATA</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="E38" s="16" t="s">
-        <v>135</v>
+        <v>9</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="12" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B39" s="7" t="str">
         <f>VLOOKUP(A39,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>EMBA ENG</v>
+        <v>IBM ENG</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>139</v>
+        <v>8</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>134</v>
@@ -16146,22 +16369,22 @@
         <v>135</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="17" t="s">
-        <v>142</v>
+      <c r="A40" s="12" t="s">
+        <v>138</v>
       </c>
       <c r="B40" s="7" t="str">
         <f>VLOOKUP(A40,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>RSC ENG</v>
+        <v>EMBA ENG</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>139</v>
@@ -16173,25 +16396,25 @@
         <v>135</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="H40" s="11" t="s">
-        <v>144</v>
+        <v>140</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
-        <v>145</v>
+      <c r="A41" s="17" t="s">
+        <v>142</v>
       </c>
       <c r="B41" s="7" t="str">
         <f>VLOOKUP(A41,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>PM ENG</v>
+        <v>RSC ENG</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>8</v>
+        <v>139</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>134</v>
@@ -16200,22 +16423,22 @@
         <v>135</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>148</v>
+        <v>144</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="18" t="s">
-        <v>149</v>
+      <c r="A42" s="12" t="s">
+        <v>145</v>
       </c>
       <c r="B42" s="7" t="str">
         <f>VLOOKUP(A42,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>MKT EC ENG</v>
+        <v>PM ENG</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>8</v>
@@ -16227,22 +16450,22 @@
         <v>135</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="H42" s="11" t="s">
-        <v>151</v>
+        <v>147</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="15" t="s">
-        <v>152</v>
+      <c r="A43" s="18" t="s">
+        <v>149</v>
       </c>
       <c r="B43" s="7" t="str">
         <f>VLOOKUP(A43,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SUPPLY ENG</v>
+        <v>MKT EC ENG</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>8</v>
@@ -16254,49 +16477,49 @@
         <v>135</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="H43" s="10" t="s">
-        <v>155</v>
+        <v>151</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
-        <v>156</v>
+      <c r="A44" s="15" t="s">
+        <v>152</v>
       </c>
       <c r="B44" s="7" t="str">
         <f>VLOOKUP(A44,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>EMBA ESP</v>
+        <v>SUPPLY ENG</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>139</v>
+        <v>8</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" s="19" t="s">
-        <v>157</v>
+        <v>134</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>135</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B45" s="7" t="str">
         <f>VLOOKUP(A45,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>GMBA</v>
+        <v>EMBA ESP</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>139</v>
@@ -16308,79 +16531,97 @@
         <v>157</v>
       </c>
       <c r="F45" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="12" t="s">
         <v>160</v>
-      </c>
-      <c r="G45" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="20" t="s">
-        <v>162</v>
       </c>
       <c r="B46" s="7" t="str">
         <f>VLOOKUP(A46,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
+        <v>GMBA</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="B47" s="7" t="str">
+        <f>VLOOKUP(A47,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
         <v>TMBA</v>
       </c>
-      <c r="C46" s="21" t="s">
+      <c r="C47" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="D46" s="21" t="s">
+      <c r="D47" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E46" s="22" t="s">
+      <c r="E47" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="F46" s="23" t="s">
+      <c r="F47" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="G46" s="24" t="s">
+      <c r="G47" s="24" t="s">
         <v>162</v>
       </c>
-      <c r="H46" s="10" t="s">
+      <c r="H47" s="10" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E48"/>
-      <c r="F48"/>
-      <c r="G48"/>
-      <c r="H48"/>
+    <row r="49" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E49"/>
+      <c r="F49"/>
+      <c r="G49"/>
+      <c r="H49"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A20">
-    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
+  <conditionalFormatting sqref="A3">
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A41:A46 A21:A22 A11:A19 A2:B2 A24:A39 A4:A9 B3:B46">
-    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
+  <conditionalFormatting sqref="A20:A21">
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A23">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  <conditionalFormatting sqref="A24">
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  <conditionalFormatting sqref="A42:A47 A22:A23 A11:A19 A2:B2 A25:A40 A4:A9 B3:B47">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
@@ -16391,9 +16632,18 @@
 </p:properties>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac690216a3feb446896882bf9e857d22">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fc1e276ee4a1c4eeb2be670671426ef6" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="95d80e3e9b41a0cd0f31651385762a39">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c785e827d86c3245c0f7c251e0c72c1" ns2:_="" ns3:_="">
     <xsd:import namespace="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
     <xsd:import namespace="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
     <xsd:element name="properties">
@@ -16627,14 +16877,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42E1AB7D-C01B-4FFE-9B42-D6ED241A40A7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C8CB7F0-A062-495C-8CF5-1C769026B7CB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -16645,21 +16887,14 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0FCCB90-18EA-419E-8607-3992FA6F6F4B}">
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42E1AB7D-C01B-4FFE-9B42-D6ED241A40A7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
-    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A732D84D-91B4-4450-ADE6-4641CDFC36C8}"/>
 </file>
--- a/Areas_Paises.xlsx
+++ b/Areas_Paises.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{A8E03CFD-D3C2-4BD9-85BF-A581898274A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{303007D5-4197-4F40-AB0E-69720AB92626}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{A8E03CFD-D3C2-4BD9-85BF-A581898274A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6876B883-8758-4835-B59E-F237D4C9A858}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{996CFF7E-4120-45EC-B5A3-4D8213062A4C}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Paises!$P$1:$V$225</definedName>
     <definedName name="PAISES">Paises!$A$1:$B$17</definedName>
     <definedName name="PILAR">Paises!$AF$1:$AG$18</definedName>
-    <definedName name="PROGRAMAS">Areas!$A$1:$G$47</definedName>
+    <definedName name="PROGRAMAS">Areas!$A$1:$G$48</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="561">
   <si>
     <t>PROGRAMA</t>
   </si>
@@ -1726,6 +1726,9 @@
   </si>
   <si>
     <t>Máster de Formación Permanente en Marketing Digital, E-commerce e Inteligencia Artificial</t>
+  </si>
+  <si>
+    <t>Máster en Transformación Digital</t>
   </si>
 </sst>
 </file>
@@ -15313,7 +15316,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451DC71D-A65B-4AC5-B117-130613ABA0E8}">
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="71.42578125" style="25" bestFit="1" customWidth="1"/>
@@ -15597,7 +15600,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>46</v>
+        <v>560</v>
       </c>
       <c r="B11" s="7" t="str">
         <f>VLOOKUP(A11,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
@@ -15624,11 +15627,11 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B12" s="7" t="str">
         <f>VLOOKUP(A12,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>OPER</v>
+        <v>TR DIGI</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>8</v>
@@ -15640,22 +15643,22 @@
         <v>10</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="B13" s="7" t="str">
         <f>VLOOKUP(A13,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>BI</v>
+        <v>OPER</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>8</v>
@@ -15667,18 +15670,18 @@
         <v>10</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>101</v>
+      <c r="A14" s="12" t="s">
+        <v>98</v>
       </c>
       <c r="B14" s="7" t="str">
         <f>VLOOKUP(A14,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
@@ -15704,12 +15707,12 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>86</v>
+      <c r="A15" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="B15" s="7" t="str">
         <f>VLOOKUP(A15,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>PROD</v>
+        <v>BI</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>8</v>
@@ -15721,22 +15724,22 @@
         <v>10</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="B16" s="7" t="str">
         <f>VLOOKUP(A16,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>BRAND</v>
+        <v>PROD</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>8</v>
@@ -15744,26 +15747,26 @@
       <c r="D16" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="13" t="s">
-        <v>55</v>
+      <c r="E16" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B17" s="7" t="str">
         <f>VLOOKUP(A17,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>COACH</v>
+        <v>BRAND</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>8</v>
@@ -15775,22 +15778,22 @@
         <v>55</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B18" s="7" t="str">
         <f>VLOOKUP(A18,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>CX</v>
+        <v>COACH</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>8</v>
@@ -15802,22 +15805,22 @@
         <v>55</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B19" s="7" t="str">
         <f>VLOOKUP(A19,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>MKT GC</v>
+        <v>CX</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>8</v>
@@ -15829,22 +15832,22 @@
         <v>55</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="93" t="s">
-        <v>550</v>
+      <c r="A20" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="B20" s="7" t="str">
         <f>VLOOKUP(A20,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>MKT EC</v>
+        <v>MKT GC</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>8</v>
@@ -15856,18 +15859,18 @@
         <v>55</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>559</v>
+      <c r="A21" s="93" t="s">
+        <v>550</v>
       </c>
       <c r="B21" s="7" t="str">
         <f>VLOOKUP(A21,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
@@ -15893,8 +15896,8 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="12" t="s">
-        <v>74</v>
+      <c r="A22" t="s">
+        <v>559</v>
       </c>
       <c r="B22" s="7" t="str">
         <f>VLOOKUP(A22,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
@@ -15921,11 +15924,11 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B23" s="7" t="str">
         <f>VLOOKUP(A23,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>NEURO MKT</v>
+        <v>MKT EC</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>8</v>
@@ -15937,22 +15940,22 @@
         <v>55</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>551</v>
+        <v>78</v>
       </c>
       <c r="B24" s="7" t="str">
         <f>VLOOKUP(A24,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>DERECHO DIG.</v>
+        <v>NEURO MKT</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>8</v>
@@ -15964,22 +15967,22 @@
         <v>55</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>552</v>
+        <v>79</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>553</v>
+        <v>80</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>554</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>82</v>
+        <v>551</v>
       </c>
       <c r="B25" s="7" t="str">
         <f>VLOOKUP(A25,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>VENTAS</v>
+        <v>DERECHO DIG.</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>8</v>
@@ -15991,22 +15994,22 @@
         <v>55</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>83</v>
+        <v>552</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>84</v>
+        <v>553</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>85</v>
+        <v>554</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="B26" s="7" t="str">
         <f>VLOOKUP(A26,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>DERECHO</v>
+        <v>VENTAS</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>8</v>
@@ -16014,26 +16017,26 @@
       <c r="D26" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="14" t="s">
-        <v>87</v>
+      <c r="E26" s="13" t="s">
+        <v>55</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="B27" s="7" t="str">
         <f>VLOOKUP(A27,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SALUD</v>
+        <v>DERECHO</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>8</v>
@@ -16045,22 +16048,22 @@
         <v>87</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="B28" s="7" t="str">
         <f>VLOOKUP(A28,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>RSC</v>
+        <v>SALUD</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>8</v>
@@ -16072,22 +16075,22 @@
         <v>87</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B29" s="7" t="str">
         <f>VLOOKUP(A29,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SOSTEN</v>
+        <v>RSC</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>8</v>
@@ -16099,22 +16102,22 @@
         <v>87</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B30" s="7" t="str">
         <f>VLOOKUP(A30,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>CIBER</v>
+        <v>SOSTEN</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>8</v>
@@ -16126,22 +16129,22 @@
         <v>87</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B31" s="7" t="str">
         <f>VLOOKUP(A31,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>GDATA</v>
+        <v>CIBER</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>8</v>
@@ -16153,22 +16156,22 @@
         <v>87</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B32" s="7" t="str">
         <f>VLOOKUP(A32,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>IA</v>
+        <v>GDATA</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>8</v>
@@ -16180,22 +16183,22 @@
         <v>87</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B33" s="7" t="str">
         <f>VLOOKUP(A33,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>PM ESP</v>
+        <v>IA</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>8</v>
@@ -16207,22 +16210,22 @@
         <v>87</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B34" s="7" t="str">
         <f>VLOOKUP(A34,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SISTEM</v>
+        <v>PM ESP</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>8</v>
@@ -16234,22 +16237,22 @@
         <v>87</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
-        <v>120</v>
+      <c r="A35" s="12" t="s">
+        <v>116</v>
       </c>
       <c r="B35" s="7" t="str">
         <f>VLOOKUP(A35,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>FULL</v>
+        <v>SISTEM</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>8</v>
@@ -16261,18 +16264,18 @@
         <v>87</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="12" t="s">
-        <v>124</v>
+      <c r="A36" s="15" t="s">
+        <v>120</v>
       </c>
       <c r="B36" s="7" t="str">
         <f>VLOOKUP(A36,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
@@ -16298,12 +16301,12 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
-        <v>125</v>
+      <c r="A37" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="B37" s="7" t="str">
         <f>VLOOKUP(A37,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>DEVOPS</v>
+        <v>FULL</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>8</v>
@@ -16315,22 +16318,22 @@
         <v>87</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B38" s="7" t="str">
         <f>VLOOKUP(A38,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>BIG DATA</v>
+        <v>DEVOPS</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>8</v>
@@ -16342,52 +16345,52 @@
         <v>87</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
-        <v>133</v>
+      <c r="A39" s="15" t="s">
+        <v>129</v>
       </c>
       <c r="B39" s="7" t="str">
         <f>VLOOKUP(A39,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>IBM ENG</v>
+        <v>BIG DATA</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="E39" s="16" t="s">
-        <v>135</v>
+        <v>9</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B40" s="7" t="str">
         <f>VLOOKUP(A40,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>EMBA ENG</v>
+        <v>IBM ENG</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>139</v>
+        <v>8</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>134</v>
@@ -16396,22 +16399,22 @@
         <v>135</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="17" t="s">
-        <v>142</v>
+      <c r="A41" s="12" t="s">
+        <v>138</v>
       </c>
       <c r="B41" s="7" t="str">
         <f>VLOOKUP(A41,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>RSC ENG</v>
+        <v>EMBA ENG</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>139</v>
@@ -16423,25 +16426,25 @@
         <v>135</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="H41" s="11" t="s">
-        <v>144</v>
+        <v>140</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>145</v>
+      <c r="A42" s="17" t="s">
+        <v>142</v>
       </c>
       <c r="B42" s="7" t="str">
         <f>VLOOKUP(A42,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>PM ENG</v>
+        <v>RSC ENG</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>8</v>
+        <v>139</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>134</v>
@@ -16450,22 +16453,22 @@
         <v>135</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="H42" s="10" t="s">
-        <v>148</v>
+        <v>144</v>
+      </c>
+      <c r="H42" s="11" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="18" t="s">
-        <v>149</v>
+      <c r="A43" s="12" t="s">
+        <v>145</v>
       </c>
       <c r="B43" s="7" t="str">
         <f>VLOOKUP(A43,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>MKT EC ENG</v>
+        <v>PM ENG</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>8</v>
@@ -16477,22 +16480,22 @@
         <v>135</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="H43" s="11" t="s">
-        <v>151</v>
+        <v>147</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="15" t="s">
-        <v>152</v>
+      <c r="A44" s="18" t="s">
+        <v>149</v>
       </c>
       <c r="B44" s="7" t="str">
         <f>VLOOKUP(A44,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SUPPLY ENG</v>
+        <v>MKT EC ENG</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>8</v>
@@ -16504,49 +16507,49 @@
         <v>135</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="H44" s="10" t="s">
-        <v>155</v>
+        <v>151</v>
+      </c>
+      <c r="H44" s="11" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="12" t="s">
-        <v>156</v>
+      <c r="A45" s="15" t="s">
+        <v>152</v>
       </c>
       <c r="B45" s="7" t="str">
         <f>VLOOKUP(A45,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>EMBA ESP</v>
+        <v>SUPPLY ENG</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>139</v>
+        <v>8</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" s="19" t="s">
-        <v>157</v>
+        <v>134</v>
+      </c>
+      <c r="E45" s="16" t="s">
+        <v>135</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B46" s="7" t="str">
         <f>VLOOKUP(A46,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>GMBA</v>
+        <v>EMBA ESP</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>139</v>
@@ -16558,63 +16561,90 @@
         <v>157</v>
       </c>
       <c r="F46" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="12" t="s">
         <v>160</v>
-      </c>
-      <c r="G46" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="20" t="s">
-        <v>162</v>
       </c>
       <c r="B47" s="7" t="str">
         <f>VLOOKUP(A47,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
+        <v>GMBA</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="G47" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="B48" s="7" t="str">
+        <f>VLOOKUP(A48,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
         <v>TMBA</v>
       </c>
-      <c r="C47" s="21" t="s">
+      <c r="C48" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="D47" s="21" t="s">
+      <c r="D48" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E47" s="22" t="s">
+      <c r="E48" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="F47" s="23" t="s">
+      <c r="F48" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="G47" s="24" t="s">
+      <c r="G48" s="24" t="s">
         <v>162</v>
       </c>
-      <c r="H47" s="10" t="s">
+      <c r="H48" s="10" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="49" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E49"/>
-      <c r="F49"/>
-      <c r="G49"/>
-      <c r="H49"/>
+    <row r="50" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E50"/>
+      <c r="F50"/>
+      <c r="G50"/>
+      <c r="H50"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A3">
     <cfRule type="duplicateValues" dxfId="7" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A20:A21">
+  <conditionalFormatting sqref="A21:A22">
     <cfRule type="duplicateValues" dxfId="6" priority="5"/>
     <cfRule type="duplicateValues" dxfId="5" priority="6"/>
     <cfRule type="duplicateValues" dxfId="4" priority="7"/>
     <cfRule type="duplicateValues" dxfId="3" priority="8"/>
     <cfRule type="duplicateValues" dxfId="2" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A24">
+  <conditionalFormatting sqref="A25">
     <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A42:A47 A22:A23 A11:A19 A2:B2 A25:A40 A4:A9 B3:B47">
+  <conditionalFormatting sqref="A43:A48 A23:A24 A12:A20 A2:B2 A26:A41 A4:A9 B3:B48">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16622,26 +16652,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="95d80e3e9b41a0cd0f31651385762a39">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c785e827d86c3245c0f7c251e0c72c1" ns2:_="" ns3:_="">
     <xsd:import namespace="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
@@ -16876,13 +16886,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C8CB7F0-A062-495C-8CF5-1C769026B7CB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A732D84D-91B4-4450-ADE6-4641CDFC36C8}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
+    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
-    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -16896,5 +16934,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A732D84D-91B4-4450-ADE6-4641CDFC36C8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C8CB7F0-A062-495C-8CF5-1C769026B7CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
+    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Areas_Paises.xlsx
+++ b/Areas_Paises.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{A8E03CFD-D3C2-4BD9-85BF-A581898274A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6876B883-8758-4835-B59E-F237D4C9A858}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{A8E03CFD-D3C2-4BD9-85BF-A581898274A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70F66592-B125-40B1-A850-2AF49EC3089D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{996CFF7E-4120-45EC-B5A3-4D8213062A4C}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Paises!$P$1:$V$225</definedName>
     <definedName name="PAISES">Paises!$A$1:$B$17</definedName>
     <definedName name="PILAR">Paises!$AF$1:$AG$18</definedName>
-    <definedName name="PROGRAMAS">Areas!$A$1:$G$48</definedName>
+    <definedName name="PROGRAMAS">Areas!$A$1:$G$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="563">
   <si>
     <t>PROGRAMA</t>
   </si>
@@ -1729,6 +1729,12 @@
   </si>
   <si>
     <t>Máster en Transformación Digital</t>
+  </si>
+  <si>
+    <t>Máster de Formación Permanente en Coaching, Liderazgo Directivo e Inteligencia Emocional</t>
+  </si>
+  <si>
+    <t>Máster de Formación Permanente en Business Intelligence &amp; Data Analytics</t>
   </si>
 </sst>
 </file>
@@ -2352,7 +2358,57 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 4" xfId="2" xr:uid="{625F2583-C0A4-468A-84E4-A45687601707}"/>
   </cellStyles>
-  <dxfs count="45">
+  <dxfs count="50">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -6825,6 +6881,54 @@
             <v>BI</v>
           </cell>
         </row>
+        <row r="389">
+          <cell r="B389" t="str">
+            <v>Lifelong Learning Master's Degree in Business Intelligence  and Data Analytics</v>
+          </cell>
+          <cell r="C389" t="str">
+            <v>BI ENG</v>
+          </cell>
+        </row>
+        <row r="390">
+          <cell r="B390" t="str">
+            <v>Lifelong Learning Master's Degree in Business Intelligence and Data Analytics</v>
+          </cell>
+          <cell r="C390" t="str">
+            <v>BI ENG</v>
+          </cell>
+        </row>
+        <row r="391">
+          <cell r="B391" t="str">
+            <v>Lifelong Learning Master’s Degree in Machine Learning and Artificial Intelligence</v>
+          </cell>
+          <cell r="C391" t="str">
+            <v>IA ENG</v>
+          </cell>
+        </row>
+        <row r="392">
+          <cell r="B392" t="str">
+            <v>Máster de Formación Permanente en Sostenibilidad, Liderazgo y RSC</v>
+          </cell>
+          <cell r="C392" t="str">
+            <v>RSC</v>
+          </cell>
+        </row>
+        <row r="393">
+          <cell r="B393" t="str">
+            <v>Lifelong Learning Master's Degree in Human Resources and Talent Management</v>
+          </cell>
+          <cell r="C393" t="str">
+            <v>RRHH ENG</v>
+          </cell>
+        </row>
+        <row r="394">
+          <cell r="B394" t="str">
+            <v>Máster de Formación Permanente en Business Intelligence &amp; Data Analytics</v>
+          </cell>
+          <cell r="C394" t="str">
+            <v>BI</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="3"/>
     </sheetDataSet>
@@ -15133,128 +15237,128 @@
     <mergeCell ref="BH32:BH41"/>
   </mergeCells>
   <conditionalFormatting sqref="A28:A30 A43:A1048576 A1:A26">
-    <cfRule type="duplicateValues" dxfId="44" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D357:D1048576 D1:D351">
-    <cfRule type="duplicateValues" dxfId="43" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P42">
-    <cfRule type="duplicateValues" dxfId="42" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P180">
-    <cfRule type="duplicateValues" dxfId="41" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P193:P194">
-    <cfRule type="duplicateValues" dxfId="40" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P196:P198">
-    <cfRule type="duplicateValues" dxfId="39" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P199">
-    <cfRule type="duplicateValues" dxfId="38" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P204">
-    <cfRule type="duplicateValues" dxfId="37" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P208">
-    <cfRule type="duplicateValues" dxfId="36" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P209">
-    <cfRule type="duplicateValues" dxfId="35" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P216 P195 P181:P184 P191:P192 P200:P203 P205:P207 P211:P212 P218:P1048576 P43:P68 P1:P11 P40 P73:P146 P13:P38 P70:P71 P148:P179">
-    <cfRule type="duplicateValues" dxfId="34" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P217">
-    <cfRule type="duplicateValues" dxfId="33" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P210:Q210">
-    <cfRule type="duplicateValues" dxfId="32" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q46">
-    <cfRule type="duplicateValues" dxfId="31" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q47">
-    <cfRule type="duplicateValues" dxfId="30" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q117">
-    <cfRule type="duplicateValues" dxfId="29" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q139">
-    <cfRule type="duplicateValues" dxfId="28" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q176">
-    <cfRule type="duplicateValues" dxfId="27" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q216:Q1048576 Q140:Q146 Q177:Q209 Q211:Q212 Q48:Q71 Q1:Q27 Q118:Q138 Q40 Q74:Q116 Q42:Q45 Q29:Q38 Q148:Q175">
-    <cfRule type="duplicateValues" dxfId="26" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R117">
-    <cfRule type="duplicateValues" dxfId="25" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R173">
-    <cfRule type="duplicateValues" dxfId="24" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R216:R1048576 R174:R212 R1:R38 R118:R146 R40 R73:R116 R42:R71 R148:R172">
-    <cfRule type="duplicateValues" dxfId="23" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="S88:T88 S97:T97 S102:T102 S104:T104 S111:T111 S115:T115 S120:T120 S127:T127 S130:T130 S133:T133 S145:T145 S156:T157 S165:T165 S174:T174">
-    <cfRule type="expression" dxfId="22" priority="29">
+    <cfRule type="expression" dxfId="27" priority="29">
       <formula>$S88=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X110">
-    <cfRule type="duplicateValues" dxfId="21" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC1:AC1048576 AI19:AI1048576">
-    <cfRule type="expression" dxfId="20" priority="34">
+    <cfRule type="expression" dxfId="25" priority="34">
       <formula>$AD1="ko"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD2:AD76 AA2:AA191">
-    <cfRule type="cellIs" dxfId="19" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="35" operator="equal">
       <formula>"ko"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="36" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AI1">
-    <cfRule type="expression" dxfId="17" priority="33">
+    <cfRule type="expression" dxfId="22" priority="33">
       <formula>$AD1="ko"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ13">
-    <cfRule type="cellIs" dxfId="16" priority="31" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="31" operator="equal">
       <formula>"ko"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="32" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AQ11:AQ21">
-    <cfRule type="duplicateValues" dxfId="14" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV21 AV25:AV29">
-    <cfRule type="cellIs" dxfId="13" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="7" operator="equal">
+      <formula>"Estudios secundarios"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="6" operator="equal">
       <formula>"Estudios primarios"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="7" operator="equal">
-      <formula>"Estudios secundarios"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW2:AW21 AW25:AW29">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="5" operator="lessThan">
       <formula>21</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AY2:AY21">
-    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="equal">
       <formula>"NOT VALID"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AY25:AY29">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="equal">
       <formula>"NOT VALID"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15279,7 +15383,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BR2:BR51">
-    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15316,7 +15420,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451DC71D-A65B-4AC5-B117-130613ABA0E8}">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="71.42578125" style="25" bestFit="1" customWidth="1"/>
@@ -15450,8 +15554,8 @@
       <c r="D5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>10</v>
+      <c r="E5" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>20</v>
@@ -15477,8 +15581,8 @@
       <c r="D6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>10</v>
+      <c r="E6" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>24</v>
@@ -15707,8 +15811,8 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>101</v>
+      <c r="A15" t="s">
+        <v>562</v>
       </c>
       <c r="B15" s="7" t="str">
         <f>VLOOKUP(A15,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
@@ -15734,12 +15838,12 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>86</v>
+      <c r="A16" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="B16" s="7" t="str">
         <f>VLOOKUP(A16,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>PROD</v>
+        <v>BI</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>8</v>
@@ -15751,22 +15855,22 @@
         <v>10</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="B17" s="7" t="str">
         <f>VLOOKUP(A17,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>BRAND</v>
+        <v>PROD</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>8</v>
@@ -15774,26 +15878,26 @@
       <c r="D17" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="13" t="s">
-        <v>55</v>
+      <c r="E17" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B18" s="7" t="str">
         <f>VLOOKUP(A18,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>COACH</v>
+        <v>BRAND</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>8</v>
@@ -15805,22 +15909,22 @@
         <v>55</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B19" s="7" t="str">
         <f>VLOOKUP(A19,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>CX</v>
+        <v>COACH</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>8</v>
@@ -15832,22 +15936,22 @@
         <v>55</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>70</v>
+      <c r="A20" s="93" t="s">
+        <v>561</v>
       </c>
       <c r="B20" s="7" t="str">
         <f>VLOOKUP(A20,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>MKT GC</v>
+        <v>COACH</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>8</v>
@@ -15859,22 +15963,22 @@
         <v>55</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="93" t="s">
-        <v>550</v>
+      <c r="A21" s="12" t="s">
+        <v>63</v>
       </c>
       <c r="B21" s="7" t="str">
         <f>VLOOKUP(A21,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>MKT EC</v>
+        <v>CX</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>8</v>
@@ -15886,22 +15990,22 @@
         <v>55</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>559</v>
+      <c r="A22" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="B22" s="7" t="str">
         <f>VLOOKUP(A22,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>MKT EC</v>
+        <v>MKT GC</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>8</v>
@@ -15913,18 +16017,18 @@
         <v>55</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>74</v>
+      <c r="A23" s="93" t="s">
+        <v>550</v>
       </c>
       <c r="B23" s="7" t="str">
         <f>VLOOKUP(A23,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
@@ -15950,12 +16054,12 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="12" t="s">
-        <v>78</v>
+      <c r="A24" t="s">
+        <v>559</v>
       </c>
       <c r="B24" s="7" t="str">
         <f>VLOOKUP(A24,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>NEURO MKT</v>
+        <v>MKT EC</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>8</v>
@@ -15967,22 +16071,22 @@
         <v>55</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>551</v>
+        <v>74</v>
       </c>
       <c r="B25" s="7" t="str">
         <f>VLOOKUP(A25,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>DERECHO DIG.</v>
+        <v>MKT EC</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>8</v>
@@ -15994,22 +16098,22 @@
         <v>55</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>552</v>
+        <v>75</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>553</v>
+        <v>76</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>554</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B26" s="7" t="str">
         <f>VLOOKUP(A26,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>VENTAS</v>
+        <v>NEURO MKT</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>8</v>
@@ -16021,22 +16125,22 @@
         <v>55</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>66</v>
+        <v>551</v>
       </c>
       <c r="B27" s="7" t="str">
         <f>VLOOKUP(A27,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>DERECHO</v>
+        <v>DERECHO DIG.</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>8</v>
@@ -16044,26 +16148,26 @@
       <c r="D27" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E27" s="14" t="s">
-        <v>87</v>
+      <c r="E27" s="13" t="s">
+        <v>55</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>67</v>
+        <v>552</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>68</v>
+        <v>553</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>69</v>
+        <v>554</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="B28" s="7" t="str">
         <f>VLOOKUP(A28,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SALUD</v>
+        <v>VENTAS</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>8</v>
@@ -16071,26 +16175,26 @@
       <c r="D28" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="14" t="s">
-        <v>87</v>
+      <c r="E28" s="13" t="s">
+        <v>55</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="B29" s="7" t="str">
         <f>VLOOKUP(A29,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>RSC</v>
+        <v>DERECHO</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>8</v>
@@ -16102,22 +16206,22 @@
         <v>87</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="B30" s="7" t="str">
         <f>VLOOKUP(A30,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SOSTEN</v>
+        <v>SALUD</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>8</v>
@@ -16129,22 +16233,22 @@
         <v>87</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B31" s="7" t="str">
         <f>VLOOKUP(A31,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>CIBER</v>
+        <v>RSC</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>8</v>
@@ -16152,26 +16256,26 @@
       <c r="D31" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E31" s="14" t="s">
-        <v>87</v>
+      <c r="E31" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B32" s="7" t="str">
         <f>VLOOKUP(A32,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>GDATA</v>
+        <v>SOSTEN</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>8</v>
@@ -16183,22 +16287,22 @@
         <v>87</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B33" s="7" t="str">
         <f>VLOOKUP(A33,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>IA</v>
+        <v>CIBER</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>8</v>
@@ -16210,22 +16314,22 @@
         <v>87</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B34" s="7" t="str">
         <f>VLOOKUP(A34,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>PM ESP</v>
+        <v>GDATA</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>8</v>
@@ -16237,22 +16341,22 @@
         <v>87</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B35" s="7" t="str">
         <f>VLOOKUP(A35,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SISTEM</v>
+        <v>IA</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>8</v>
@@ -16264,22 +16368,22 @@
         <v>87</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
-        <v>120</v>
+      <c r="A36" s="12" t="s">
+        <v>112</v>
       </c>
       <c r="B36" s="7" t="str">
         <f>VLOOKUP(A36,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>FULL</v>
+        <v>PM ESP</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>8</v>
@@ -16291,22 +16395,22 @@
         <v>87</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="B37" s="7" t="str">
         <f>VLOOKUP(A37,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>FULL</v>
+        <v>SISTEM</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>8</v>
@@ -16318,22 +16422,22 @@
         <v>87</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B38" s="7" t="str">
         <f>VLOOKUP(A38,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>DEVOPS</v>
+        <v>FULL</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>8</v>
@@ -16345,22 +16449,22 @@
         <v>87</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="15" t="s">
-        <v>129</v>
+      <c r="A39" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="B39" s="7" t="str">
         <f>VLOOKUP(A39,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>BIG DATA</v>
+        <v>FULL</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>8</v>
@@ -16372,79 +16476,79 @@
         <v>87</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
-        <v>133</v>
+      <c r="A40" s="15" t="s">
+        <v>125</v>
       </c>
       <c r="B40" s="7" t="str">
         <f>VLOOKUP(A40,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>IBM ENG</v>
+        <v>DEVOPS</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="E40" s="16" t="s">
-        <v>135</v>
+        <v>9</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="12" t="s">
-        <v>138</v>
+      <c r="A41" s="15" t="s">
+        <v>129</v>
       </c>
       <c r="B41" s="7" t="str">
         <f>VLOOKUP(A41,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>EMBA ENG</v>
+        <v>BIG DATA</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>139</v>
+        <v>8</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="E41" s="16" t="s">
-        <v>135</v>
+        <v>9</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="17" t="s">
-        <v>142</v>
+      <c r="A42" s="12" t="s">
+        <v>133</v>
       </c>
       <c r="B42" s="7" t="str">
         <f>VLOOKUP(A42,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>RSC ENG</v>
+        <v>IBM ENG</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>139</v>
+        <v>8</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>134</v>
@@ -16453,25 +16557,25 @@
         <v>135</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="H42" s="11" t="s">
-        <v>144</v>
+        <v>137</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B43" s="7" t="str">
         <f>VLOOKUP(A43,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>PM ENG</v>
+        <v>EMBA ENG</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>8</v>
+        <v>139</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>134</v>
@@ -16480,25 +16584,25 @@
         <v>135</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="18" t="s">
-        <v>149</v>
+      <c r="A44" s="17" t="s">
+        <v>142</v>
       </c>
       <c r="B44" s="7" t="str">
         <f>VLOOKUP(A44,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>MKT EC ENG</v>
+        <v>RSC ENG</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>8</v>
+        <v>139</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>134</v>
@@ -16507,22 +16611,22 @@
         <v>135</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="15" t="s">
-        <v>152</v>
+      <c r="A45" s="12" t="s">
+        <v>145</v>
       </c>
       <c r="B45" s="7" t="str">
         <f>VLOOKUP(A45,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SUPPLY ENG</v>
+        <v>PM ENG</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>8</v>
@@ -16534,124 +16638,205 @@
         <v>135</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="12" t="s">
-        <v>156</v>
+      <c r="A46" s="18" t="s">
+        <v>149</v>
       </c>
       <c r="B46" s="7" t="str">
         <f>VLOOKUP(A46,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>EMBA ESP</v>
+        <v>MKT EC ENG</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>139</v>
+        <v>8</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" s="19" t="s">
-        <v>157</v>
+        <v>134</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>135</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>159</v>
+        <v>151</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="12" t="s">
-        <v>160</v>
+      <c r="A47" s="15" t="s">
+        <v>152</v>
       </c>
       <c r="B47" s="7" t="str">
         <f>VLOOKUP(A47,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>GMBA</v>
+        <v>SUPPLY ENG</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>139</v>
+        <v>8</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E47" s="19" t="s">
-        <v>157</v>
+        <v>134</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>135</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="20" t="s">
-        <v>162</v>
+      <c r="A48" s="12" t="s">
+        <v>156</v>
       </c>
       <c r="B48" s="7" t="str">
         <f>VLOOKUP(A48,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
+        <v>EMBA ESP</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="G48" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="B49" s="7" t="str">
+        <f>VLOOKUP(A49,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
+        <v>GMBA</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="B50" s="7" t="str">
+        <f>VLOOKUP(A50,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
         <v>TMBA</v>
       </c>
-      <c r="C48" s="21" t="s">
+      <c r="C50" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="D48" s="21" t="s">
+      <c r="D50" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E48" s="22" t="s">
+      <c r="E50" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="F48" s="23" t="s">
+      <c r="F50" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="G48" s="24" t="s">
+      <c r="G50" s="24" t="s">
         <v>162</v>
       </c>
-      <c r="H48" s="10" t="s">
+      <c r="H50" s="10" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="50" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E50"/>
-      <c r="F50"/>
-      <c r="G50"/>
-      <c r="H50"/>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E52"/>
+      <c r="F52"/>
+      <c r="G52"/>
+      <c r="H52"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A3">
-    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A21:A22">
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="9"/>
+  <conditionalFormatting sqref="A20">
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A25">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+  <conditionalFormatting sqref="A23:A24">
+    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A43:A48 A23:A24 A12:A20 A2:B2 A26:A41 A4:A9 B3:B48">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  <conditionalFormatting sqref="A27">
+    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A45:A50 A25:A26 A12:A14 A2:B2 A28:A43 A4:A9 A21:A22 A16:A19 B3:B50">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="95d80e3e9b41a0cd0f31651385762a39">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c785e827d86c3245c0f7c251e0c72c1" ns2:_="" ns3:_="">
     <xsd:import namespace="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
@@ -16886,27 +17071,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42E1AB7D-C01B-4FFE-9B42-D6ED241A40A7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C8CB7F0-A062-495C-8CF5-1C769026B7CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
+    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A732D84D-91B4-4450-ADE6-4641CDFC36C8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16923,23 +17107,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42E1AB7D-C01B-4FFE-9B42-D6ED241A40A7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C8CB7F0-A062-495C-8CF5-1C769026B7CB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
-    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Areas_Paises.xlsx
+++ b/Areas_Paises.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{A8E03CFD-D3C2-4BD9-85BF-A581898274A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70F66592-B125-40B1-A850-2AF49EC3089D}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="13_ncr:1_{A8E03CFD-D3C2-4BD9-85BF-A581898274A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48F903F3-F0EA-47A0-812A-65A3C85D5C27}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{996CFF7E-4120-45EC-B5A3-4D8213062A4C}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{996CFF7E-4120-45EC-B5A3-4D8213062A4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Paises" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Paises!$P$1:$V$225</definedName>
     <definedName name="PAISES">Paises!$A$1:$B$17</definedName>
     <definedName name="PILAR">Paises!$AF$1:$AG$18</definedName>
-    <definedName name="PROGRAMAS">Areas!$A$1:$G$50</definedName>
+    <definedName name="PROGRAMAS">Areas!$A$1:$G$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="566">
   <si>
     <t>PROGRAMA</t>
   </si>
@@ -1735,6 +1735,15 @@
   </si>
   <si>
     <t>Máster de Formación Permanente en Business Intelligence &amp; Data Analytics</t>
+  </si>
+  <si>
+    <t>Lifelong Learning Master's Degree in Business Intelligence and Data Analytics</t>
+  </si>
+  <si>
+    <t>Business Intelligence y Analytics (ENG)</t>
+  </si>
+  <si>
+    <t>BI (ENG)</t>
   </si>
 </sst>
 </file>
@@ -6929,6 +6938,14 @@
             <v>BI</v>
           </cell>
         </row>
+        <row r="395">
+          <cell r="B395" t="str">
+            <v>Master in Business Intelligence and Analytics</v>
+          </cell>
+          <cell r="C395" t="str">
+            <v>BI</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="3"/>
     </sheetDataSet>
@@ -15340,11 +15357,11 @@
     <cfRule type="duplicateValues" dxfId="19" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV21 AV25:AV29">
-    <cfRule type="cellIs" dxfId="18" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="6" operator="equal">
+      <formula>"Estudios primarios"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
       <formula>"Estudios secundarios"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="6" operator="equal">
-      <formula>"Estudios primarios"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW2:AW21 AW25:AW29">
@@ -15420,7 +15437,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451DC71D-A65B-4AC5-B117-130613ABA0E8}">
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="71.42578125" style="25" bestFit="1" customWidth="1"/>
@@ -16648,12 +16665,12 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="18" t="s">
-        <v>149</v>
+      <c r="A46" s="25" t="s">
+        <v>563</v>
       </c>
       <c r="B46" s="7" t="str">
         <f>VLOOKUP(A46,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>MKT EC ENG</v>
+        <v>BI ENG</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>8</v>
@@ -16665,22 +16682,22 @@
         <v>135</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>150</v>
+        <v>564</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>151</v>
+        <v>565</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="15" t="s">
-        <v>152</v>
+        <v>565</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="18" t="s">
+        <v>149</v>
       </c>
       <c r="B47" s="7" t="str">
         <f>VLOOKUP(A47,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SUPPLY ENG</v>
+        <v>MKT EC ENG</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>8</v>
@@ -16692,49 +16709,49 @@
         <v>135</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>155</v>
+        <v>151</v>
+      </c>
+      <c r="H47" s="11" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="12" t="s">
-        <v>156</v>
+      <c r="A48" s="15" t="s">
+        <v>152</v>
       </c>
       <c r="B48" s="7" t="str">
         <f>VLOOKUP(A48,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>EMBA ESP</v>
+        <v>SUPPLY ENG</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>139</v>
+        <v>8</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E48" s="19" t="s">
-        <v>157</v>
+        <v>134</v>
+      </c>
+      <c r="E48" s="16" t="s">
+        <v>135</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B49" s="7" t="str">
         <f>VLOOKUP(A49,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>GMBA</v>
+        <v>EMBA ESP</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>139</v>
@@ -16746,47 +16763,74 @@
         <v>157</v>
       </c>
       <c r="F49" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="12" t="s">
         <v>160</v>
-      </c>
-      <c r="G49" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="20" t="s">
-        <v>162</v>
       </c>
       <c r="B50" s="7" t="str">
         <f>VLOOKUP(A50,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
+        <v>GMBA</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="B51" s="7" t="str">
+        <f>VLOOKUP(A51,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
         <v>TMBA</v>
       </c>
-      <c r="C50" s="21" t="s">
+      <c r="C51" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="D50" s="21" t="s">
+      <c r="D51" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E50" s="22" t="s">
+      <c r="E51" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="F50" s="23" t="s">
+      <c r="F51" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="G50" s="24" t="s">
+      <c r="G51" s="24" t="s">
         <v>162</v>
       </c>
-      <c r="H50" s="10" t="s">
+      <c r="H51" s="10" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E52"/>
-      <c r="F52"/>
-      <c r="G52"/>
-      <c r="H52"/>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E53"/>
+      <c r="F53"/>
+      <c r="G53"/>
+      <c r="H53"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A3">
@@ -16809,7 +16853,7 @@
   <conditionalFormatting sqref="A27">
     <cfRule type="duplicateValues" dxfId="1" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A45:A50 A25:A26 A12:A14 A2:B2 A28:A43 A4:A9 A21:A22 A16:A19 B3:B50">
+  <conditionalFormatting sqref="A25:A26 A12:A14 A2:B2 A28:A43 A4:A9 A21:A22 A16:A19 A45 A47:A51 B3:B51">
     <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16826,17 +16870,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="95d80e3e9b41a0cd0f31651385762a39">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c785e827d86c3245c0f7c251e0c72c1" ns2:_="" ns3:_="">
     <xsd:import namespace="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
@@ -17071,6 +17104,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42E1AB7D-C01B-4FFE-9B42-D6ED241A40A7}">
   <ds:schemaRefs>
@@ -17080,17 +17124,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C8CB7F0-A062-495C-8CF5-1C769026B7CB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
-    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A732D84D-91B4-4450-ADE6-4641CDFC36C8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17107,4 +17140,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C8CB7F0-A062-495C-8CF5-1C769026B7CB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
+    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Areas_Paises.xlsx
+++ b/Areas_Paises.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="13_ncr:1_{A8E03CFD-D3C2-4BD9-85BF-A581898274A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48F903F3-F0EA-47A0-812A-65A3C85D5C27}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="13_ncr:1_{A8E03CFD-D3C2-4BD9-85BF-A581898274A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D1F1FD3-0B54-4495-A00D-10024BDBB009}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{996CFF7E-4120-45EC-B5A3-4D8213062A4C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{996CFF7E-4120-45EC-B5A3-4D8213062A4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Paises" sheetId="2" r:id="rId1"/>
@@ -15357,11 +15357,11 @@
     <cfRule type="duplicateValues" dxfId="19" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV21 AV25:AV29">
-    <cfRule type="cellIs" dxfId="18" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="7" operator="equal">
+      <formula>"Estudios secundarios"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="6" operator="equal">
       <formula>"Estudios primarios"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
-      <formula>"Estudios secundarios"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW2:AW21 AW25:AW29">
@@ -15544,8 +15544,8 @@
       <c r="D4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>10</v>
+      <c r="E4" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>16</v>
@@ -15652,8 +15652,8 @@
       <c r="D8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>10</v>
+      <c r="E8" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>32</v>
@@ -16003,8 +16003,8 @@
       <c r="D21" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="13" t="s">
-        <v>55</v>
+      <c r="E21" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>64</v>
@@ -16850,23 +16850,25 @@
     <cfRule type="duplicateValues" dxfId="3" priority="13"/>
     <cfRule type="duplicateValues" dxfId="2" priority="14"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A25:A26 A12:A14 A2:B2 A28:A43 A4:A9 A21:A22 A16:A19 A45 A47:A51 B3:B51">
+    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A27">
-    <cfRule type="duplicateValues" dxfId="1" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A25:A26 A12:A14 A2:B2 A28:A43 A4:A9 A21:A22 A16:A19 A45 A47:A51 B3:B51">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17105,20 +17107,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="e4f8e1ef-7590-4615-a0b0-41d92864fb7e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42E1AB7D-C01B-4FFE-9B42-D6ED241A40A7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C8CB7F0-A062-495C-8CF5-1C769026B7CB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
+    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -17143,12 +17146,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C8CB7F0-A062-495C-8CF5-1C769026B7CB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42E1AB7D-C01B-4FFE-9B42-D6ED241A40A7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
-    <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Areas_Paises.xlsx
+++ b/Areas_Paises.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="13_ncr:1_{A8E03CFD-D3C2-4BD9-85BF-A581898274A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D1F1FD3-0B54-4495-A00D-10024BDBB009}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="13_ncr:1_{A8E03CFD-D3C2-4BD9-85BF-A581898274A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9429A3B-3137-4017-9A98-ACE0D898C23A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{996CFF7E-4120-45EC-B5A3-4D8213062A4C}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Paises!$P$1:$V$225</definedName>
     <definedName name="PAISES">Paises!$A$1:$B$17</definedName>
     <definedName name="PILAR">Paises!$AF$1:$AG$18</definedName>
-    <definedName name="PROGRAMAS">Areas!$A$1:$G$51</definedName>
+    <definedName name="PROGRAMAS">Areas!$A$1:$G$52</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="567">
   <si>
     <t>PROGRAMA</t>
   </si>
@@ -1744,6 +1744,9 @@
   </si>
   <si>
     <t>BI (ENG)</t>
+  </si>
+  <si>
+    <t>Máster de Formación Permanente en Sostenibilidad, Liderazgo y RSC</t>
   </si>
 </sst>
 </file>
@@ -6943,7 +6946,7 @@
             <v>Master in Business Intelligence and Analytics</v>
           </cell>
           <cell r="C395" t="str">
-            <v>BI</v>
+            <v>BI ENG</v>
           </cell>
         </row>
       </sheetData>
@@ -15437,7 +15440,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451DC71D-A65B-4AC5-B117-130613ABA0E8}">
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="71.42578125" style="25" bestFit="1" customWidth="1"/>
@@ -15544,8 +15547,8 @@
       <c r="D4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="14" t="s">
-        <v>87</v>
+      <c r="E4" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>16</v>
@@ -15571,8 +15574,8 @@
       <c r="D5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="14" t="s">
-        <v>87</v>
+      <c r="E5" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>20</v>
@@ -16261,7 +16264,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>91</v>
+        <v>566</v>
       </c>
       <c r="B31" s="7" t="str">
         <f>VLOOKUP(A31,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
@@ -16288,11 +16291,11 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B32" s="7" t="str">
         <f>VLOOKUP(A32,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SOSTEN</v>
+        <v>RSC</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>8</v>
@@ -16300,26 +16303,26 @@
       <c r="D32" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E32" s="14" t="s">
-        <v>87</v>
+      <c r="E32" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B33" s="7" t="str">
         <f>VLOOKUP(A33,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>CIBER</v>
+        <v>SOSTEN</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>8</v>
@@ -16331,22 +16334,22 @@
         <v>87</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B34" s="7" t="str">
         <f>VLOOKUP(A34,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>GDATA</v>
+        <v>CIBER</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>8</v>
@@ -16358,22 +16361,22 @@
         <v>87</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B35" s="7" t="str">
         <f>VLOOKUP(A35,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>IA</v>
+        <v>GDATA</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>8</v>
@@ -16385,22 +16388,22 @@
         <v>87</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B36" s="7" t="str">
         <f>VLOOKUP(A36,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>PM ESP</v>
+        <v>IA</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>8</v>
@@ -16412,22 +16415,22 @@
         <v>87</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B37" s="7" t="str">
         <f>VLOOKUP(A37,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SISTEM</v>
+        <v>PM ESP</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>8</v>
@@ -16439,22 +16442,22 @@
         <v>87</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
-        <v>120</v>
+      <c r="A38" s="12" t="s">
+        <v>116</v>
       </c>
       <c r="B38" s="7" t="str">
         <f>VLOOKUP(A38,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>FULL</v>
+        <v>SISTEM</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>8</v>
@@ -16466,18 +16469,18 @@
         <v>87</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="12" t="s">
-        <v>124</v>
+      <c r="A39" s="15" t="s">
+        <v>120</v>
       </c>
       <c r="B39" s="7" t="str">
         <f>VLOOKUP(A39,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
@@ -16503,12 +16506,12 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="15" t="s">
-        <v>125</v>
+      <c r="A40" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="B40" s="7" t="str">
         <f>VLOOKUP(A40,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>DEVOPS</v>
+        <v>FULL</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>8</v>
@@ -16520,22 +16523,22 @@
         <v>87</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B41" s="7" t="str">
         <f>VLOOKUP(A41,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>BIG DATA</v>
+        <v>DEVOPS</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>8</v>
@@ -16547,52 +16550,52 @@
         <v>87</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="12" t="s">
-        <v>133</v>
+      <c r="A42" s="15" t="s">
+        <v>129</v>
       </c>
       <c r="B42" s="7" t="str">
         <f>VLOOKUP(A42,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>IBM ENG</v>
+        <v>BIG DATA</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="E42" s="16" t="s">
-        <v>135</v>
+        <v>9</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="12" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B43" s="7" t="str">
         <f>VLOOKUP(A43,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>EMBA ENG</v>
+        <v>IBM ENG</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>139</v>
+        <v>8</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>134</v>
@@ -16601,22 +16604,22 @@
         <v>135</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="17" t="s">
-        <v>142</v>
+      <c r="A44" s="12" t="s">
+        <v>138</v>
       </c>
       <c r="B44" s="7" t="str">
         <f>VLOOKUP(A44,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>RSC ENG</v>
+        <v>EMBA ENG</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>139</v>
@@ -16628,25 +16631,25 @@
         <v>135</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="H44" s="11" t="s">
-        <v>144</v>
+        <v>140</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="12" t="s">
-        <v>145</v>
+      <c r="A45" s="17" t="s">
+        <v>142</v>
       </c>
       <c r="B45" s="7" t="str">
         <f>VLOOKUP(A45,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>PM ENG</v>
+        <v>RSC ENG</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>8</v>
+        <v>139</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>134</v>
@@ -16655,22 +16658,22 @@
         <v>135</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="H45" s="10" t="s">
-        <v>148</v>
+        <v>144</v>
+      </c>
+      <c r="H45" s="11" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="25" t="s">
-        <v>563</v>
+      <c r="A46" s="12" t="s">
+        <v>145</v>
       </c>
       <c r="B46" s="7" t="str">
         <f>VLOOKUP(A46,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>BI ENG</v>
+        <v>PM ENG</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>8</v>
@@ -16682,22 +16685,22 @@
         <v>135</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>564</v>
+        <v>146</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>565</v>
-      </c>
-      <c r="H46" s="11" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="18" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="25" t="s">
+        <v>563</v>
       </c>
       <c r="B47" s="7" t="str">
         <f>VLOOKUP(A47,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>MKT EC ENG</v>
+        <v>BI ENG</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>8</v>
@@ -16709,22 +16712,22 @@
         <v>135</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>150</v>
+        <v>564</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>151</v>
+        <v>565</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="15" t="s">
-        <v>152</v>
+        <v>565</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="18" t="s">
+        <v>149</v>
       </c>
       <c r="B48" s="7" t="str">
         <f>VLOOKUP(A48,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SUPPLY ENG</v>
+        <v>MKT EC ENG</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>8</v>
@@ -16736,49 +16739,49 @@
         <v>135</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="H48" s="10" t="s">
-        <v>155</v>
+        <v>151</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
-        <v>156</v>
+      <c r="A49" s="15" t="s">
+        <v>152</v>
       </c>
       <c r="B49" s="7" t="str">
         <f>VLOOKUP(A49,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>EMBA ESP</v>
+        <v>SUPPLY ENG</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>139</v>
+        <v>8</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E49" s="19" t="s">
-        <v>157</v>
+        <v>134</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>135</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B50" s="7" t="str">
         <f>VLOOKUP(A50,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>GMBA</v>
+        <v>EMBA ESP</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>139</v>
@@ -16790,47 +16793,74 @@
         <v>157</v>
       </c>
       <c r="F50" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="G50" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="12" t="s">
         <v>160</v>
-      </c>
-      <c r="G50" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="H50" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="20" t="s">
-        <v>162</v>
       </c>
       <c r="B51" s="7" t="str">
         <f>VLOOKUP(A51,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
+        <v>GMBA</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="B52" s="7" t="str">
+        <f>VLOOKUP(A52,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
         <v>TMBA</v>
       </c>
-      <c r="C51" s="21" t="s">
+      <c r="C52" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="D51" s="21" t="s">
+      <c r="D52" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E51" s="22" t="s">
+      <c r="E52" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="F51" s="23" t="s">
+      <c r="F52" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="G51" s="24" t="s">
+      <c r="G52" s="24" t="s">
         <v>162</v>
       </c>
-      <c r="H51" s="10" t="s">
+      <c r="H52" s="10" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E53"/>
-      <c r="F53"/>
-      <c r="G53"/>
-      <c r="H53"/>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E54"/>
+      <c r="F54"/>
+      <c r="G54"/>
+      <c r="H54"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A3">
@@ -16850,7 +16880,7 @@
     <cfRule type="duplicateValues" dxfId="3" priority="13"/>
     <cfRule type="duplicateValues" dxfId="2" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A25:A26 A12:A14 A2:B2 A28:A43 A4:A9 A21:A22 A16:A19 A45 A47:A51 B3:B51">
+  <conditionalFormatting sqref="A25:A26 A12:A14 A2:B2 A28:A44 A4:A9 A21:A22 A16:A19 A46 A48:A52 B3:B52">
     <cfRule type="duplicateValues" dxfId="1" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
@@ -16861,6 +16891,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
@@ -16871,7 +16910,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A62BD1A1B5CAC249A95BCCCA1576DD25" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="95d80e3e9b41a0cd0f31651385762a39">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="e4f8e1ef-7590-4615-a0b0-41d92864fb7e" xmlns:ns3="396b9688-3d64-4f4f-b40d-59fd809f50b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c785e827d86c3245c0f7c251e0c72c1" ns2:_="" ns3:_="">
     <xsd:import namespace="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
@@ -17106,16 +17145,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42E1AB7D-C01B-4FFE-9B42-D6ED241A40A7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C8CB7F0-A062-495C-8CF5-1C769026B7CB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -17126,7 +17164,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A732D84D-91B4-4450-ADE6-4641CDFC36C8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17143,12 +17181,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42E1AB7D-C01B-4FFE-9B42-D6ED241A40A7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Areas_Paises.xlsx
+++ b/Areas_Paises.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gplaneta.sharepoint.com/sites/BIPOWER/Shared Documents/General/Distribución Atenea/Codigos/Distribución OBS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="13_ncr:1_{A8E03CFD-D3C2-4BD9-85BF-A581898274A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9429A3B-3137-4017-9A98-ACE0D898C23A}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="13_ncr:1_{A8E03CFD-D3C2-4BD9-85BF-A581898274A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAAF1677-DBA0-4A2B-9691-A6B99EBAC6F9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{996CFF7E-4120-45EC-B5A3-4D8213062A4C}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Paises!$P$1:$V$225</definedName>
     <definedName name="PAISES">Paises!$A$1:$B$17</definedName>
     <definedName name="PILAR">Paises!$AF$1:$AG$18</definedName>
-    <definedName name="PROGRAMAS">Areas!$A$1:$G$52</definedName>
+    <definedName name="PROGRAMAS">Areas!$A$1:$G$53</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="568">
   <si>
     <t>PROGRAMA</t>
   </si>
@@ -1747,6 +1747,9 @@
   </si>
   <si>
     <t>Máster de Formación Permanente en Sostenibilidad, Liderazgo y RSC</t>
+  </si>
+  <si>
+    <t>Máster de Formación Permanente en Transformación Digital</t>
   </si>
 </sst>
 </file>
@@ -15360,11 +15363,11 @@
     <cfRule type="duplicateValues" dxfId="19" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AV2:AV21 AV25:AV29">
-    <cfRule type="cellIs" dxfId="18" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="6" operator="equal">
+      <formula>"Estudios primarios"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
       <formula>"Estudios secundarios"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="6" operator="equal">
-      <formula>"Estudios primarios"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW2:AW21 AW25:AW29">
@@ -15440,7 +15443,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451DC71D-A65B-4AC5-B117-130613ABA0E8}">
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="71.42578125" style="25" bestFit="1" customWidth="1"/>
@@ -15750,8 +15753,8 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>46</v>
+      <c r="A12" t="s">
+        <v>567</v>
       </c>
       <c r="B12" s="7" t="str">
         <f>VLOOKUP(A12,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
@@ -15778,11 +15781,11 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B13" s="7" t="str">
         <f>VLOOKUP(A13,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>OPER</v>
+        <v>TR DIGI</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>8</v>
@@ -15794,22 +15797,22 @@
         <v>10</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="B14" s="7" t="str">
         <f>VLOOKUP(A14,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>BI</v>
+        <v>OPER</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>8</v>
@@ -15821,18 +15824,18 @@
         <v>10</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>562</v>
+      <c r="A15" s="12" t="s">
+        <v>98</v>
       </c>
       <c r="B15" s="7" t="str">
         <f>VLOOKUP(A15,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
@@ -15858,8 +15861,8 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>101</v>
+      <c r="A16" t="s">
+        <v>562</v>
       </c>
       <c r="B16" s="7" t="str">
         <f>VLOOKUP(A16,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
@@ -15885,12 +15888,12 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
-        <v>86</v>
+      <c r="A17" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="B17" s="7" t="str">
         <f>VLOOKUP(A17,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>PROD</v>
+        <v>BI</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>8</v>
@@ -15902,22 +15905,22 @@
         <v>10</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="B18" s="7" t="str">
         <f>VLOOKUP(A18,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>BRAND</v>
+        <v>PROD</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>8</v>
@@ -15925,26 +15928,26 @@
       <c r="D18" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="13" t="s">
-        <v>55</v>
+      <c r="E18" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B19" s="7" t="str">
         <f>VLOOKUP(A19,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>COACH</v>
+        <v>BRAND</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>8</v>
@@ -15956,18 +15959,18 @@
         <v>55</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="93" t="s">
-        <v>561</v>
+      <c r="A20" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="B20" s="7" t="str">
         <f>VLOOKUP(A20,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
@@ -15993,12 +15996,12 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>63</v>
+      <c r="A21" s="93" t="s">
+        <v>561</v>
       </c>
       <c r="B21" s="7" t="str">
         <f>VLOOKUP(A21,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>CX</v>
+        <v>COACH</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>8</v>
@@ -16006,26 +16009,26 @@
       <c r="D21" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="14" t="s">
-        <v>87</v>
+      <c r="E21" s="13" t="s">
+        <v>55</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B22" s="7" t="str">
         <f>VLOOKUP(A22,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>MKT GC</v>
+        <v>CX</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>8</v>
@@ -16033,26 +16036,26 @@
       <c r="D22" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>55</v>
+      <c r="E22" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="93" t="s">
-        <v>550</v>
+      <c r="A23" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="B23" s="7" t="str">
         <f>VLOOKUP(A23,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>MKT EC</v>
+        <v>MKT GC</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>8</v>
@@ -16064,18 +16067,18 @@
         <v>55</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>559</v>
+      <c r="A24" s="93" t="s">
+        <v>550</v>
       </c>
       <c r="B24" s="7" t="str">
         <f>VLOOKUP(A24,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
@@ -16101,8 +16104,8 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
-        <v>74</v>
+      <c r="A25" t="s">
+        <v>559</v>
       </c>
       <c r="B25" s="7" t="str">
         <f>VLOOKUP(A25,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
@@ -16129,11 +16132,11 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B26" s="7" t="str">
         <f>VLOOKUP(A26,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>NEURO MKT</v>
+        <v>MKT EC</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>8</v>
@@ -16145,22 +16148,22 @@
         <v>55</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>551</v>
+        <v>78</v>
       </c>
       <c r="B27" s="7" t="str">
         <f>VLOOKUP(A27,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>DERECHO DIG.</v>
+        <v>NEURO MKT</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>8</v>
@@ -16172,22 +16175,22 @@
         <v>55</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>552</v>
+        <v>79</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>553</v>
+        <v>80</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>554</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>82</v>
+        <v>551</v>
       </c>
       <c r="B28" s="7" t="str">
         <f>VLOOKUP(A28,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>VENTAS</v>
+        <v>DERECHO DIG.</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>8</v>
@@ -16199,22 +16202,22 @@
         <v>55</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>83</v>
+        <v>552</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>84</v>
+        <v>553</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>85</v>
+        <v>554</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="B29" s="7" t="str">
         <f>VLOOKUP(A29,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>DERECHO</v>
+        <v>VENTAS</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>8</v>
@@ -16222,26 +16225,26 @@
       <c r="D29" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="14" t="s">
-        <v>87</v>
+      <c r="E29" s="13" t="s">
+        <v>55</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="B30" s="7" t="str">
         <f>VLOOKUP(A30,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SALUD</v>
+        <v>DERECHO</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>8</v>
@@ -16253,22 +16256,22 @@
         <v>87</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>566</v>
+        <v>42</v>
       </c>
       <c r="B31" s="7" t="str">
         <f>VLOOKUP(A31,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>RSC</v>
+        <v>SALUD</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>8</v>
@@ -16276,22 +16279,22 @@
       <c r="D31" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E31" s="9" t="s">
-        <v>10</v>
+      <c r="E31" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>91</v>
+        <v>566</v>
       </c>
       <c r="B32" s="7" t="str">
         <f>VLOOKUP(A32,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
@@ -16318,11 +16321,11 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B33" s="7" t="str">
         <f>VLOOKUP(A33,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SOSTEN</v>
+        <v>RSC</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>8</v>
@@ -16330,26 +16333,26 @@
       <c r="D33" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E33" s="14" t="s">
-        <v>87</v>
+      <c r="E33" s="9" t="s">
+        <v>10</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B34" s="7" t="str">
         <f>VLOOKUP(A34,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>CIBER</v>
+        <v>SOSTEN</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>8</v>
@@ -16361,22 +16364,22 @@
         <v>87</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="12" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B35" s="7" t="str">
         <f>VLOOKUP(A35,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>GDATA</v>
+        <v>CIBER</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>8</v>
@@ -16388,22 +16391,22 @@
         <v>87</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B36" s="7" t="str">
         <f>VLOOKUP(A36,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>IA</v>
+        <v>GDATA</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>8</v>
@@ -16415,22 +16418,22 @@
         <v>87</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B37" s="7" t="str">
         <f>VLOOKUP(A37,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>PM ESP</v>
+        <v>IA</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>8</v>
@@ -16442,22 +16445,22 @@
         <v>87</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B38" s="7" t="str">
         <f>VLOOKUP(A38,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SISTEM</v>
+        <v>PM ESP</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>8</v>
@@ -16469,22 +16472,22 @@
         <v>87</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="15" t="s">
-        <v>120</v>
+      <c r="A39" s="12" t="s">
+        <v>116</v>
       </c>
       <c r="B39" s="7" t="str">
         <f>VLOOKUP(A39,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>FULL</v>
+        <v>SISTEM</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>8</v>
@@ -16496,18 +16499,18 @@
         <v>87</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
-        <v>124</v>
+      <c r="A40" s="15" t="s">
+        <v>120</v>
       </c>
       <c r="B40" s="7" t="str">
         <f>VLOOKUP(A40,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
@@ -16533,12 +16536,12 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
-        <v>125</v>
+      <c r="A41" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="B41" s="7" t="str">
         <f>VLOOKUP(A41,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>DEVOPS</v>
+        <v>FULL</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>8</v>
@@ -16550,22 +16553,22 @@
         <v>87</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B42" s="7" t="str">
         <f>VLOOKUP(A42,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>BIG DATA</v>
+        <v>DEVOPS</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>8</v>
@@ -16577,52 +16580,52 @@
         <v>87</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
-        <v>133</v>
+      <c r="A43" s="15" t="s">
+        <v>129</v>
       </c>
       <c r="B43" s="7" t="str">
         <f>VLOOKUP(A43,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>IBM ENG</v>
+        <v>BIG DATA</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="E43" s="16" t="s">
-        <v>135</v>
+        <v>9</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>87</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B44" s="7" t="str">
         <f>VLOOKUP(A44,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>EMBA ENG</v>
+        <v>IBM ENG</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>139</v>
+        <v>8</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>134</v>
@@ -16631,22 +16634,22 @@
         <v>135</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="17" t="s">
-        <v>142</v>
+      <c r="A45" s="12" t="s">
+        <v>138</v>
       </c>
       <c r="B45" s="7" t="str">
         <f>VLOOKUP(A45,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>RSC ENG</v>
+        <v>EMBA ENG</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>139</v>
@@ -16658,25 +16661,25 @@
         <v>135</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="H45" s="11" t="s">
-        <v>144</v>
+        <v>140</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="12" t="s">
-        <v>145</v>
+      <c r="A46" s="17" t="s">
+        <v>142</v>
       </c>
       <c r="B46" s="7" t="str">
         <f>VLOOKUP(A46,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>PM ENG</v>
+        <v>RSC ENG</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>8</v>
+        <v>139</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>134</v>
@@ -16685,22 +16688,22 @@
         <v>135</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="H46" s="10" t="s">
-        <v>148</v>
+        <v>144</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="25" t="s">
-        <v>563</v>
+      <c r="A47" s="12" t="s">
+        <v>145</v>
       </c>
       <c r="B47" s="7" t="str">
         <f>VLOOKUP(A47,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>BI ENG</v>
+        <v>PM ENG</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>8</v>
@@ -16712,22 +16715,22 @@
         <v>135</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>564</v>
+        <v>146</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>565</v>
-      </c>
-      <c r="H47" s="11" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="18" t="s">
-        <v>149</v>
+        <v>147</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="25" t="s">
+        <v>563</v>
       </c>
       <c r="B48" s="7" t="str">
         <f>VLOOKUP(A48,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>MKT EC ENG</v>
+        <v>BI ENG</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>8</v>
@@ -16739,22 +16742,22 @@
         <v>135</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>150</v>
+        <v>564</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>151</v>
+        <v>565</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="15" t="s">
-        <v>152</v>
+        <v>565</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="18" t="s">
+        <v>149</v>
       </c>
       <c r="B49" s="7" t="str">
         <f>VLOOKUP(A49,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>SUPPLY ENG</v>
+        <v>MKT EC ENG</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>8</v>
@@ -16766,49 +16769,49 @@
         <v>135</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="H49" s="10" t="s">
-        <v>155</v>
+        <v>151</v>
+      </c>
+      <c r="H49" s="11" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
-        <v>156</v>
+      <c r="A50" s="15" t="s">
+        <v>152</v>
       </c>
       <c r="B50" s="7" t="str">
         <f>VLOOKUP(A50,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>EMBA ESP</v>
+        <v>SUPPLY ENG</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>139</v>
+        <v>8</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E50" s="19" t="s">
-        <v>157</v>
+        <v>134</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>135</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B51" s="7" t="str">
         <f>VLOOKUP(A51,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
-        <v>GMBA</v>
+        <v>EMBA ESP</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>139</v>
@@ -16820,70 +16823,97 @@
         <v>157</v>
       </c>
       <c r="F51" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="12" t="s">
         <v>160</v>
-      </c>
-      <c r="G51" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="H51" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="20" t="s">
-        <v>162</v>
       </c>
       <c r="B52" s="7" t="str">
         <f>VLOOKUP(A52,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
+        <v>GMBA</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="G52" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="H52" s="10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="B53" s="7" t="str">
+        <f>VLOOKUP(A53,'[1]NORMALIZACION PROGRAMAS'!$B:$C,2,0)</f>
         <v>TMBA</v>
       </c>
-      <c r="C52" s="21" t="s">
+      <c r="C53" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="D52" s="21" t="s">
+      <c r="D53" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E52" s="22" t="s">
+      <c r="E53" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="F52" s="23" t="s">
+      <c r="F53" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="G52" s="24" t="s">
+      <c r="G53" s="24" t="s">
         <v>162</v>
       </c>
-      <c r="H52" s="10" t="s">
+      <c r="H53" s="10" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E54"/>
-      <c r="F54"/>
-      <c r="G54"/>
-      <c r="H54"/>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E55"/>
+      <c r="F55"/>
+      <c r="G55"/>
+      <c r="H55"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A3">
     <cfRule type="duplicateValues" dxfId="12" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A20">
+  <conditionalFormatting sqref="A21">
     <cfRule type="duplicateValues" dxfId="11" priority="1"/>
     <cfRule type="duplicateValues" dxfId="10" priority="2"/>
     <cfRule type="duplicateValues" dxfId="9" priority="3"/>
     <cfRule type="duplicateValues" dxfId="8" priority="4"/>
     <cfRule type="duplicateValues" dxfId="7" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A23:A24">
+  <conditionalFormatting sqref="A24:A25">
     <cfRule type="duplicateValues" dxfId="6" priority="10"/>
     <cfRule type="duplicateValues" dxfId="5" priority="11"/>
     <cfRule type="duplicateValues" dxfId="4" priority="12"/>
     <cfRule type="duplicateValues" dxfId="3" priority="13"/>
     <cfRule type="duplicateValues" dxfId="2" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A25:A26 A12:A14 A2:B2 A28:A44 A4:A9 A21:A22 A16:A19 A46 A48:A52 B3:B52">
+  <conditionalFormatting sqref="A26:A27 A13:A15 A2:B2 A29:A45 A4:A9 A22:A23 A17:A20 A47 A49:A53 B3:B53">
     <cfRule type="duplicateValues" dxfId="1" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A27">
+  <conditionalFormatting sqref="A28">
     <cfRule type="duplicateValues" dxfId="0" priority="9"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16891,15 +16921,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="396b9688-3d64-4f4f-b40d-59fd809f50b1" xsi:nil="true"/>
@@ -16908,6 +16929,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17146,20 +17176,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42E1AB7D-C01B-4FFE-9B42-D6ED241A40A7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C8CB7F0-A062-495C-8CF5-1C769026B7CB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="396b9688-3d64-4f4f-b40d-59fd809f50b1"/>
     <ds:schemaRef ds:uri="e4f8e1ef-7590-4615-a0b0-41d92864fb7e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42E1AB7D-C01B-4FFE-9B42-D6ED241A40A7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
